--- a/apps/backend/excel-data/holidaystudentsub_library_migration.xlsx
+++ b/apps/backend/excel-data/holidaystudentsub_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="410">
   <si>
     <t>legacy_id</t>
   </si>
@@ -32,6 +32,1215 @@
   </si>
   <si>
     <t>2026-06-01T04:06:03.622Z</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>migration returned no result</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:24.588Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:25.593Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:26.544Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:27.449Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:28.476Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:29.943Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:30.856Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:31.934Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:33.004Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:35.810Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:37.428Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:38.427Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:40.302Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:41.555Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:42.863Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:44.307Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:45.810Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:47.633Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:49.739Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:53.381Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:56.012Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:57.799Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:52:59.642Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:01.947Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:05.379Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:07.504Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:10.486Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:12.547Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:15.874Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:18.777Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:20.323Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:21.942Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:24.070Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:25.848Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:27.210Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:29.006Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:31.067Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:32.647Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:34.523Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:35.886Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:37.701Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:39.153Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:40.604Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:42.207Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:43.892Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:45.205Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:46.919Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:48.637Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:50.491Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:51.900Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:53.298Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:54.941Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:56.291Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:57.594Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:53:58.986Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:00.521Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:01.937Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:03.400Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:04.836Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:06.355Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:07.417Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:08.762Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:10.156Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:11.582Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:13.109Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:14.282Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:15.896Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:16.980Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:18.339Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:19.718Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:21.255Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:22.634Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:24.091Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:25.571Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:27.042Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:28.856Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:30.328Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:31.721Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:33.154Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:34.585Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:36.227Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:37.982Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:39.440Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:40.795Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:42.179Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:43.628Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:45.343Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:46.636Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:47.815Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:49.245Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:50.327Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:51.806Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:53.390Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:54.843Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:56.641Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:57.960Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:54:58.998Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:00.355Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:01.964Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:03.342Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:04.662Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:06.186Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:07.651Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:09.015Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:10.299Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:11.557Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:12.980Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:14.286Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:15.710Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:16.998Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:17.942Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:19.555Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:20.927Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:22.282Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:23.720Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:24.796Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:26.108Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:27.171Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:28.520Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:29.902Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:31.159Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:32.424Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:33.715Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:35.103Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:36.418Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:37.751Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:39.088Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:40.412Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:41.709Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:43.074Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:44.415Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:45.760Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:47.073Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:48.388Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:49.435Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:50.763Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:51.727Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:53.124Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:54.560Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:55.906Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:57.311Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:58.327Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:55:59.357Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:00.399Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:01.372Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:02.424Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:03.553Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:04.551Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:05.605Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:06.632Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:07.666Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:11.029Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:12.155Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:13.176Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:14.197Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:15.195Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:16.373Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:17.486Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:18.467Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:19.526Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:20.548Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:21.575Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:22.596Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:23.628Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:24.636Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:25.660Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:26.689Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:27.717Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:28.786Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:29.730Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:30.801Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:31.770Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:32.817Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:34.090Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:35.094Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:36.447Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:37.859Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:39.194Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:40.520Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:41.851Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:43.082Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:44.410Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:45.746Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:47.170Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:48.324Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:49.605Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:50.864Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:52.188Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:53.525Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:54.538Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:55.756Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:57.012Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:58.336Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:56:59.664Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:00.691Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:02.023Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:02.980Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:04.203Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:05.515Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:06.778Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:07.989Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:09.195Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:10.503Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:11.983Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:13.167Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:14.379Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:15.653Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:16.887Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:18.123Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:19.334Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:20.530Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:21.811Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:23.125Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:24.415Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:25.593Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:26.781Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:28.094Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:29.062Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:30.264Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:31.176Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:32.479Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:33.719Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:34.911Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:36.135Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:37.439Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:38.407Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:39.673Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:40.944Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:42.157Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:43.397Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:44.574Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:45.861Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:47.125Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:48.371Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:49.619Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:50.915Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:52.114Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:53.433Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:54.642Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:55.587Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:56.770Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:57.940Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:57:59.119Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:00.366Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:01.306Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:02.472Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:03.344Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:04.561Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:05.716Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:07.024Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:08.268Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:09.517Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:10.834Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:12.193Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:13.424Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:14.721Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:15.970Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:17.169Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:18.389Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:19.596Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:21.028Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:22.314Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:23.581Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:24.516Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:25.723Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:26.651Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:27.865Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:29.171Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:30.373Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:31.596Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:32.558Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:33.475Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:34.482Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:35.426Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:36.412Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:37.336Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:38.244Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:39.264Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:40.289Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:41.268Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:42.205Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:43.128Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:44.101Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:45.131Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:46.030Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:46.944Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:47.914Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:48.901Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:49.861Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:50.887Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:51.897Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:52.914Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:53.911Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:54.962Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:55.986Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:57.034Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:58.039Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:58:59.070Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:00.058Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:00.935Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:01.903Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:02.949Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:04.313Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:05.309Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:06.617Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:07.876Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:09.176Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:10.440Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:11.773Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:13.098Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:14.428Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:15.734Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:17.071Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:18.318Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:19.656Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:20.987Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:22.209Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:23.537Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:24.522Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:25.759Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:27.035Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:28.352Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:29.684Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:30.693Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:31.935Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:32.853Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:34.188Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:35.518Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:36.752Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:38.100Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:39.414Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:40.723Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:42.074Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:43.415Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:44.734Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:46.077Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:47.400Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:48.749Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:50.077Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:51.365Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:52.631Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:53.960Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:55.268Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:56.613Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:57.962Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:59:59.383Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:00.421Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:01.721Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:02.830Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:04.199Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:05.634Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:06.957Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:08.301Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:09.629Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:10.641Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:11.980Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:13.315Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:14.643Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:15.940Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:17.177Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:18.442Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:19.779Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:21.093Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:22.323Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:23.653Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:24.985Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:26.320Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:27.688Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:28.675Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:30.109Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:31.603Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:33.011Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:34.426Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:35.439Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:36.765Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:37.783Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:39.148Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:40.553Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:41.861Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:43.218Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:44.543Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:45.878Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:47.209Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:48.433Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:49.771Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:51.077Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:52.331Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:53.661Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:54.996Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:56.331Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:57.761Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:00:59.004Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:01:00.009Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:01:01.313Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:01:02.361Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:01:03.698Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:01:05.026Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:01:06.361Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:01:07.687Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:01:08.706Z</t>
+  </si>
+  <si>
+    <t>2026-06-19T06:01:09.733Z</t>
   </si>
 </sst>
 </file>
@@ -412,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D403"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -443,8 +1652,5622 @@
         <v>6</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>91</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>110</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>457</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>458</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>459</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>460</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>461</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>462</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>463</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>464</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>465</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>466</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>467</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>468</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>469</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>470</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>471</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>472</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>473</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>474</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>475</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>476</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>477</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>478</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>479</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>480</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>481</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>482</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>483</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>484</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>485</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>486</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>487</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>488</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>489</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>490</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>491</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>492</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>493</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>494</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>495</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>496</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>497</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>498</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>499</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>500</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>501</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>502</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>503</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>504</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>505</v>
+      </c>
+      <c r="B63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>506</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>507</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>508</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>509</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>510</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>511</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>512</v>
+      </c>
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>513</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>514</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>515</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>516</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>517</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>518</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>519</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>520</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>521</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>522</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>523</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>524</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>525</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>526</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>527</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>528</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>529</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>530</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>531</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>532</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>533</v>
+      </c>
+      <c r="B91" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>534</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>535</v>
+      </c>
+      <c r="B93" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>536</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>537</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>538</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>539</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>540</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>541</v>
+      </c>
+      <c r="B99" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>542</v>
+      </c>
+      <c r="B100" t="s">
+        <v>4</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>543</v>
+      </c>
+      <c r="B101" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>544</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>545</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>546</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+      <c r="D104" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>547</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+      <c r="D105" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>548</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>549</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>550</v>
+      </c>
+      <c r="B108" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>551</v>
+      </c>
+      <c r="B109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>552</v>
+      </c>
+      <c r="B110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>553</v>
+      </c>
+      <c r="B111" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>554</v>
+      </c>
+      <c r="B112" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>555</v>
+      </c>
+      <c r="B113" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>556</v>
+      </c>
+      <c r="B114" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>557</v>
+      </c>
+      <c r="B115" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>558</v>
+      </c>
+      <c r="B116" t="s">
+        <v>4</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>559</v>
+      </c>
+      <c r="B117" t="s">
+        <v>4</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>560</v>
+      </c>
+      <c r="B118" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>561</v>
+      </c>
+      <c r="B119" t="s">
+        <v>4</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>562</v>
+      </c>
+      <c r="B120" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>563</v>
+      </c>
+      <c r="B121" t="s">
+        <v>4</v>
+      </c>
+      <c r="C121" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>564</v>
+      </c>
+      <c r="B122" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>565</v>
+      </c>
+      <c r="B123" t="s">
+        <v>4</v>
+      </c>
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>566</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4</v>
+      </c>
+      <c r="C124" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>567</v>
+      </c>
+      <c r="B125" t="s">
+        <v>4</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>568</v>
+      </c>
+      <c r="B126" t="s">
+        <v>4</v>
+      </c>
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>569</v>
+      </c>
+      <c r="B127" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>570</v>
+      </c>
+      <c r="B128" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>571</v>
+      </c>
+      <c r="B129" t="s">
+        <v>4</v>
+      </c>
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>572</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>573</v>
+      </c>
+      <c r="B131" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>574</v>
+      </c>
+      <c r="B132" t="s">
+        <v>4</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>575</v>
+      </c>
+      <c r="B133" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>576</v>
+      </c>
+      <c r="B134" t="s">
+        <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>577</v>
+      </c>
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>578</v>
+      </c>
+      <c r="B136" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>579</v>
+      </c>
+      <c r="B137" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" t="s">
+        <v>8</v>
+      </c>
+      <c r="D137" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>580</v>
+      </c>
+      <c r="B138" t="s">
+        <v>4</v>
+      </c>
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>581</v>
+      </c>
+      <c r="B139" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>582</v>
+      </c>
+      <c r="B140" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" t="s">
+        <v>5</v>
+      </c>
+      <c r="D140" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>583</v>
+      </c>
+      <c r="B141" t="s">
+        <v>4</v>
+      </c>
+      <c r="C141" t="s">
+        <v>5</v>
+      </c>
+      <c r="D141" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>584</v>
+      </c>
+      <c r="B142" t="s">
+        <v>4</v>
+      </c>
+      <c r="C142" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>585</v>
+      </c>
+      <c r="B143" t="s">
+        <v>4</v>
+      </c>
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>586</v>
+      </c>
+      <c r="B144" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>587</v>
+      </c>
+      <c r="B145" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" t="s">
+        <v>8</v>
+      </c>
+      <c r="D145" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>588</v>
+      </c>
+      <c r="B146" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" t="s">
+        <v>8</v>
+      </c>
+      <c r="D146" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>589</v>
+      </c>
+      <c r="B147" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>590</v>
+      </c>
+      <c r="B148" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>591</v>
+      </c>
+      <c r="B149" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>592</v>
+      </c>
+      <c r="B150" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>593</v>
+      </c>
+      <c r="B151" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>594</v>
+      </c>
+      <c r="B152" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>595</v>
+      </c>
+      <c r="B153" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>596</v>
+      </c>
+      <c r="B154" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>597</v>
+      </c>
+      <c r="B155" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>598</v>
+      </c>
+      <c r="B156" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>599</v>
+      </c>
+      <c r="B157" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>600</v>
+      </c>
+      <c r="B158" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>601</v>
+      </c>
+      <c r="B159" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>602</v>
+      </c>
+      <c r="B160" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>603</v>
+      </c>
+      <c r="B161" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>604</v>
+      </c>
+      <c r="B162" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>605</v>
+      </c>
+      <c r="B163" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>606</v>
+      </c>
+      <c r="B164" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>607</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>608</v>
+      </c>
+      <c r="B166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>609</v>
+      </c>
+      <c r="B167" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>610</v>
+      </c>
+      <c r="B168" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>611</v>
+      </c>
+      <c r="B169" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>612</v>
+      </c>
+      <c r="B170" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>613</v>
+      </c>
+      <c r="B171" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>614</v>
+      </c>
+      <c r="B172" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>615</v>
+      </c>
+      <c r="B173" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>616</v>
+      </c>
+      <c r="B174" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>617</v>
+      </c>
+      <c r="B175" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>618</v>
+      </c>
+      <c r="B176" t="s">
+        <v>4</v>
+      </c>
+      <c r="C176" t="s">
+        <v>5</v>
+      </c>
+      <c r="D176" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>619</v>
+      </c>
+      <c r="B177" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>620</v>
+      </c>
+      <c r="B178" t="s">
+        <v>4</v>
+      </c>
+      <c r="C178" t="s">
+        <v>5</v>
+      </c>
+      <c r="D178" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>621</v>
+      </c>
+      <c r="B179" t="s">
+        <v>4</v>
+      </c>
+      <c r="C179" t="s">
+        <v>5</v>
+      </c>
+      <c r="D179" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>622</v>
+      </c>
+      <c r="B180" t="s">
+        <v>4</v>
+      </c>
+      <c r="C180" t="s">
+        <v>5</v>
+      </c>
+      <c r="D180" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>623</v>
+      </c>
+      <c r="B181" t="s">
+        <v>4</v>
+      </c>
+      <c r="C181" t="s">
+        <v>5</v>
+      </c>
+      <c r="D181" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>624</v>
+      </c>
+      <c r="B182" t="s">
+        <v>4</v>
+      </c>
+      <c r="C182" t="s">
+        <v>5</v>
+      </c>
+      <c r="D182" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>625</v>
+      </c>
+      <c r="B183" t="s">
+        <v>4</v>
+      </c>
+      <c r="C183" t="s">
+        <v>5</v>
+      </c>
+      <c r="D183" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>626</v>
+      </c>
+      <c r="B184" t="s">
+        <v>4</v>
+      </c>
+      <c r="C184" t="s">
+        <v>5</v>
+      </c>
+      <c r="D184" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>627</v>
+      </c>
+      <c r="B185" t="s">
+        <v>4</v>
+      </c>
+      <c r="C185" t="s">
+        <v>5</v>
+      </c>
+      <c r="D185" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>628</v>
+      </c>
+      <c r="B186" t="s">
+        <v>4</v>
+      </c>
+      <c r="C186" t="s">
+        <v>5</v>
+      </c>
+      <c r="D186" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>629</v>
+      </c>
+      <c r="B187" t="s">
+        <v>4</v>
+      </c>
+      <c r="C187" t="s">
+        <v>5</v>
+      </c>
+      <c r="D187" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>630</v>
+      </c>
+      <c r="B188" t="s">
+        <v>4</v>
+      </c>
+      <c r="C188" t="s">
+        <v>5</v>
+      </c>
+      <c r="D188" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>631</v>
+      </c>
+      <c r="B189" t="s">
+        <v>4</v>
+      </c>
+      <c r="C189" t="s">
+        <v>5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>632</v>
+      </c>
+      <c r="B190" t="s">
+        <v>4</v>
+      </c>
+      <c r="C190" t="s">
+        <v>5</v>
+      </c>
+      <c r="D190" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>633</v>
+      </c>
+      <c r="B191" t="s">
+        <v>4</v>
+      </c>
+      <c r="C191" t="s">
+        <v>5</v>
+      </c>
+      <c r="D191" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>634</v>
+      </c>
+      <c r="B192" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192" t="s">
+        <v>8</v>
+      </c>
+      <c r="D192" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>635</v>
+      </c>
+      <c r="B193" t="s">
+        <v>4</v>
+      </c>
+      <c r="C193" t="s">
+        <v>5</v>
+      </c>
+      <c r="D193" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>636</v>
+      </c>
+      <c r="B194" t="s">
+        <v>4</v>
+      </c>
+      <c r="C194" t="s">
+        <v>5</v>
+      </c>
+      <c r="D194" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>637</v>
+      </c>
+      <c r="B195" t="s">
+        <v>4</v>
+      </c>
+      <c r="C195" t="s">
+        <v>5</v>
+      </c>
+      <c r="D195" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>638</v>
+      </c>
+      <c r="B196" t="s">
+        <v>4</v>
+      </c>
+      <c r="C196" t="s">
+        <v>5</v>
+      </c>
+      <c r="D196" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>639</v>
+      </c>
+      <c r="B197" t="s">
+        <v>7</v>
+      </c>
+      <c r="C197" t="s">
+        <v>8</v>
+      </c>
+      <c r="D197" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>640</v>
+      </c>
+      <c r="B198" t="s">
+        <v>4</v>
+      </c>
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>641</v>
+      </c>
+      <c r="B199" t="s">
+        <v>7</v>
+      </c>
+      <c r="C199" t="s">
+        <v>8</v>
+      </c>
+      <c r="D199" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>642</v>
+      </c>
+      <c r="B200" t="s">
+        <v>4</v>
+      </c>
+      <c r="C200" t="s">
+        <v>5</v>
+      </c>
+      <c r="D200" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>643</v>
+      </c>
+      <c r="B201" t="s">
+        <v>4</v>
+      </c>
+      <c r="C201" t="s">
+        <v>5</v>
+      </c>
+      <c r="D201" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>644</v>
+      </c>
+      <c r="B202" t="s">
+        <v>4</v>
+      </c>
+      <c r="C202" t="s">
+        <v>5</v>
+      </c>
+      <c r="D202" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>645</v>
+      </c>
+      <c r="B203" t="s">
+        <v>4</v>
+      </c>
+      <c r="C203" t="s">
+        <v>5</v>
+      </c>
+      <c r="D203" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>646</v>
+      </c>
+      <c r="B204" t="s">
+        <v>4</v>
+      </c>
+      <c r="C204" t="s">
+        <v>5</v>
+      </c>
+      <c r="D204" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>647</v>
+      </c>
+      <c r="B205" t="s">
+        <v>4</v>
+      </c>
+      <c r="C205" t="s">
+        <v>5</v>
+      </c>
+      <c r="D205" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>648</v>
+      </c>
+      <c r="B206" t="s">
+        <v>4</v>
+      </c>
+      <c r="C206" t="s">
+        <v>5</v>
+      </c>
+      <c r="D206" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>649</v>
+      </c>
+      <c r="B207" t="s">
+        <v>4</v>
+      </c>
+      <c r="C207" t="s">
+        <v>5</v>
+      </c>
+      <c r="D207" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>650</v>
+      </c>
+      <c r="B208" t="s">
+        <v>4</v>
+      </c>
+      <c r="C208" t="s">
+        <v>5</v>
+      </c>
+      <c r="D208" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>651</v>
+      </c>
+      <c r="B209" t="s">
+        <v>4</v>
+      </c>
+      <c r="C209" t="s">
+        <v>5</v>
+      </c>
+      <c r="D209" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>652</v>
+      </c>
+      <c r="B210" t="s">
+        <v>4</v>
+      </c>
+      <c r="C210" t="s">
+        <v>5</v>
+      </c>
+      <c r="D210" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>653</v>
+      </c>
+      <c r="B211" t="s">
+        <v>4</v>
+      </c>
+      <c r="C211" t="s">
+        <v>5</v>
+      </c>
+      <c r="D211" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>654</v>
+      </c>
+      <c r="B212" t="s">
+        <v>4</v>
+      </c>
+      <c r="C212" t="s">
+        <v>5</v>
+      </c>
+      <c r="D212" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>655</v>
+      </c>
+      <c r="B213" t="s">
+        <v>4</v>
+      </c>
+      <c r="C213" t="s">
+        <v>5</v>
+      </c>
+      <c r="D213" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>656</v>
+      </c>
+      <c r="B214" t="s">
+        <v>4</v>
+      </c>
+      <c r="C214" t="s">
+        <v>5</v>
+      </c>
+      <c r="D214" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>657</v>
+      </c>
+      <c r="B215" t="s">
+        <v>4</v>
+      </c>
+      <c r="C215" t="s">
+        <v>5</v>
+      </c>
+      <c r="D215" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>658</v>
+      </c>
+      <c r="B216" t="s">
+        <v>4</v>
+      </c>
+      <c r="C216" t="s">
+        <v>5</v>
+      </c>
+      <c r="D216" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>659</v>
+      </c>
+      <c r="B217" t="s">
+        <v>4</v>
+      </c>
+      <c r="C217" t="s">
+        <v>5</v>
+      </c>
+      <c r="D217" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>660</v>
+      </c>
+      <c r="B218" t="s">
+        <v>4</v>
+      </c>
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>661</v>
+      </c>
+      <c r="B219" t="s">
+        <v>4</v>
+      </c>
+      <c r="C219" t="s">
+        <v>5</v>
+      </c>
+      <c r="D219" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>662</v>
+      </c>
+      <c r="B220" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" t="s">
+        <v>8</v>
+      </c>
+      <c r="D220" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>663</v>
+      </c>
+      <c r="B221" t="s">
+        <v>4</v>
+      </c>
+      <c r="C221" t="s">
+        <v>5</v>
+      </c>
+      <c r="D221" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>664</v>
+      </c>
+      <c r="B222" t="s">
+        <v>7</v>
+      </c>
+      <c r="C222" t="s">
+        <v>8</v>
+      </c>
+      <c r="D222" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>665</v>
+      </c>
+      <c r="B223" t="s">
+        <v>4</v>
+      </c>
+      <c r="C223" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>666</v>
+      </c>
+      <c r="B224" t="s">
+        <v>4</v>
+      </c>
+      <c r="C224" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>667</v>
+      </c>
+      <c r="B225" t="s">
+        <v>4</v>
+      </c>
+      <c r="C225" t="s">
+        <v>5</v>
+      </c>
+      <c r="D225" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>668</v>
+      </c>
+      <c r="B226" t="s">
+        <v>4</v>
+      </c>
+      <c r="C226" t="s">
+        <v>5</v>
+      </c>
+      <c r="D226" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>669</v>
+      </c>
+      <c r="B227" t="s">
+        <v>4</v>
+      </c>
+      <c r="C227" t="s">
+        <v>5</v>
+      </c>
+      <c r="D227" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>670</v>
+      </c>
+      <c r="B228" t="s">
+        <v>7</v>
+      </c>
+      <c r="C228" t="s">
+        <v>8</v>
+      </c>
+      <c r="D228" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>671</v>
+      </c>
+      <c r="B229" t="s">
+        <v>4</v>
+      </c>
+      <c r="C229" t="s">
+        <v>5</v>
+      </c>
+      <c r="D229" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>672</v>
+      </c>
+      <c r="B230" t="s">
+        <v>4</v>
+      </c>
+      <c r="C230" t="s">
+        <v>5</v>
+      </c>
+      <c r="D230" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>673</v>
+      </c>
+      <c r="B231" t="s">
+        <v>4</v>
+      </c>
+      <c r="C231" t="s">
+        <v>5</v>
+      </c>
+      <c r="D231" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>674</v>
+      </c>
+      <c r="B232" t="s">
+        <v>4</v>
+      </c>
+      <c r="C232" t="s">
+        <v>5</v>
+      </c>
+      <c r="D232" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>675</v>
+      </c>
+      <c r="B233" t="s">
+        <v>4</v>
+      </c>
+      <c r="C233" t="s">
+        <v>5</v>
+      </c>
+      <c r="D233" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>676</v>
+      </c>
+      <c r="B234" t="s">
+        <v>4</v>
+      </c>
+      <c r="C234" t="s">
+        <v>5</v>
+      </c>
+      <c r="D234" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>677</v>
+      </c>
+      <c r="B235" t="s">
+        <v>4</v>
+      </c>
+      <c r="C235" t="s">
+        <v>5</v>
+      </c>
+      <c r="D235" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>678</v>
+      </c>
+      <c r="B236" t="s">
+        <v>4</v>
+      </c>
+      <c r="C236" t="s">
+        <v>5</v>
+      </c>
+      <c r="D236" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>679</v>
+      </c>
+      <c r="B237" t="s">
+        <v>4</v>
+      </c>
+      <c r="C237" t="s">
+        <v>5</v>
+      </c>
+      <c r="D237" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>680</v>
+      </c>
+      <c r="B238" t="s">
+        <v>4</v>
+      </c>
+      <c r="C238" t="s">
+        <v>5</v>
+      </c>
+      <c r="D238" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>681</v>
+      </c>
+      <c r="B239" t="s">
+        <v>4</v>
+      </c>
+      <c r="C239" t="s">
+        <v>5</v>
+      </c>
+      <c r="D239" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>682</v>
+      </c>
+      <c r="B240" t="s">
+        <v>4</v>
+      </c>
+      <c r="C240" t="s">
+        <v>5</v>
+      </c>
+      <c r="D240" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>683</v>
+      </c>
+      <c r="B241" t="s">
+        <v>4</v>
+      </c>
+      <c r="C241" t="s">
+        <v>5</v>
+      </c>
+      <c r="D241" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>684</v>
+      </c>
+      <c r="B242" t="s">
+        <v>7</v>
+      </c>
+      <c r="C242" t="s">
+        <v>8</v>
+      </c>
+      <c r="D242" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>685</v>
+      </c>
+      <c r="B243" t="s">
+        <v>4</v>
+      </c>
+      <c r="C243" t="s">
+        <v>5</v>
+      </c>
+      <c r="D243" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>686</v>
+      </c>
+      <c r="B244" t="s">
+        <v>4</v>
+      </c>
+      <c r="C244" t="s">
+        <v>5</v>
+      </c>
+      <c r="D244" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>687</v>
+      </c>
+      <c r="B245" t="s">
+        <v>4</v>
+      </c>
+      <c r="C245" t="s">
+        <v>5</v>
+      </c>
+      <c r="D245" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>688</v>
+      </c>
+      <c r="B246" t="s">
+        <v>4</v>
+      </c>
+      <c r="C246" t="s">
+        <v>5</v>
+      </c>
+      <c r="D246" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>689</v>
+      </c>
+      <c r="B247" t="s">
+        <v>7</v>
+      </c>
+      <c r="C247" t="s">
+        <v>8</v>
+      </c>
+      <c r="D247" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>690</v>
+      </c>
+      <c r="B248" t="s">
+        <v>4</v>
+      </c>
+      <c r="C248" t="s">
+        <v>5</v>
+      </c>
+      <c r="D248" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>691</v>
+      </c>
+      <c r="B249" t="s">
+        <v>7</v>
+      </c>
+      <c r="C249" t="s">
+        <v>8</v>
+      </c>
+      <c r="D249" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>692</v>
+      </c>
+      <c r="B250" t="s">
+        <v>4</v>
+      </c>
+      <c r="C250" t="s">
+        <v>5</v>
+      </c>
+      <c r="D250" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>693</v>
+      </c>
+      <c r="B251" t="s">
+        <v>4</v>
+      </c>
+      <c r="C251" t="s">
+        <v>5</v>
+      </c>
+      <c r="D251" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>694</v>
+      </c>
+      <c r="B252" t="s">
+        <v>4</v>
+      </c>
+      <c r="C252" t="s">
+        <v>5</v>
+      </c>
+      <c r="D252" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>695</v>
+      </c>
+      <c r="B253" t="s">
+        <v>4</v>
+      </c>
+      <c r="C253" t="s">
+        <v>5</v>
+      </c>
+      <c r="D253" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>696</v>
+      </c>
+      <c r="B254" t="s">
+        <v>4</v>
+      </c>
+      <c r="C254" t="s">
+        <v>5</v>
+      </c>
+      <c r="D254" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>697</v>
+      </c>
+      <c r="B255" t="s">
+        <v>4</v>
+      </c>
+      <c r="C255" t="s">
+        <v>5</v>
+      </c>
+      <c r="D255" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>698</v>
+      </c>
+      <c r="B256" t="s">
+        <v>4</v>
+      </c>
+      <c r="C256" t="s">
+        <v>5</v>
+      </c>
+      <c r="D256" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>699</v>
+      </c>
+      <c r="B257" t="s">
+        <v>4</v>
+      </c>
+      <c r="C257" t="s">
+        <v>5</v>
+      </c>
+      <c r="D257" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>700</v>
+      </c>
+      <c r="B258" t="s">
+        <v>4</v>
+      </c>
+      <c r="C258" t="s">
+        <v>5</v>
+      </c>
+      <c r="D258" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>701</v>
+      </c>
+      <c r="B259" t="s">
+        <v>4</v>
+      </c>
+      <c r="C259" t="s">
+        <v>5</v>
+      </c>
+      <c r="D259" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>702</v>
+      </c>
+      <c r="B260" t="s">
+        <v>4</v>
+      </c>
+      <c r="C260" t="s">
+        <v>5</v>
+      </c>
+      <c r="D260" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>703</v>
+      </c>
+      <c r="B261" t="s">
+        <v>4</v>
+      </c>
+      <c r="C261" t="s">
+        <v>5</v>
+      </c>
+      <c r="D261" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>704</v>
+      </c>
+      <c r="B262" t="s">
+        <v>4</v>
+      </c>
+      <c r="C262" t="s">
+        <v>5</v>
+      </c>
+      <c r="D262" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>705</v>
+      </c>
+      <c r="B263" t="s">
+        <v>4</v>
+      </c>
+      <c r="C263" t="s">
+        <v>5</v>
+      </c>
+      <c r="D263" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>706</v>
+      </c>
+      <c r="B264" t="s">
+        <v>4</v>
+      </c>
+      <c r="C264" t="s">
+        <v>5</v>
+      </c>
+      <c r="D264" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>707</v>
+      </c>
+      <c r="B265" t="s">
+        <v>4</v>
+      </c>
+      <c r="C265" t="s">
+        <v>5</v>
+      </c>
+      <c r="D265" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>708</v>
+      </c>
+      <c r="B266" t="s">
+        <v>7</v>
+      </c>
+      <c r="C266" t="s">
+        <v>8</v>
+      </c>
+      <c r="D266" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>709</v>
+      </c>
+      <c r="B267" t="s">
+        <v>4</v>
+      </c>
+      <c r="C267" t="s">
+        <v>5</v>
+      </c>
+      <c r="D267" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>710</v>
+      </c>
+      <c r="B268" t="s">
+        <v>7</v>
+      </c>
+      <c r="C268" t="s">
+        <v>8</v>
+      </c>
+      <c r="D268" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>711</v>
+      </c>
+      <c r="B269" t="s">
+        <v>4</v>
+      </c>
+      <c r="C269" t="s">
+        <v>5</v>
+      </c>
+      <c r="D269" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>712</v>
+      </c>
+      <c r="B270" t="s">
+        <v>4</v>
+      </c>
+      <c r="C270" t="s">
+        <v>5</v>
+      </c>
+      <c r="D270" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>713</v>
+      </c>
+      <c r="B271" t="s">
+        <v>4</v>
+      </c>
+      <c r="C271" t="s">
+        <v>5</v>
+      </c>
+      <c r="D271" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>714</v>
+      </c>
+      <c r="B272" t="s">
+        <v>4</v>
+      </c>
+      <c r="C272" t="s">
+        <v>5</v>
+      </c>
+      <c r="D272" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>715</v>
+      </c>
+      <c r="B273" t="s">
+        <v>7</v>
+      </c>
+      <c r="C273" t="s">
+        <v>8</v>
+      </c>
+      <c r="D273" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>716</v>
+      </c>
+      <c r="B274" t="s">
+        <v>7</v>
+      </c>
+      <c r="C274" t="s">
+        <v>8</v>
+      </c>
+      <c r="D274" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>717</v>
+      </c>
+      <c r="B275" t="s">
+        <v>7</v>
+      </c>
+      <c r="C275" t="s">
+        <v>8</v>
+      </c>
+      <c r="D275" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>718</v>
+      </c>
+      <c r="B276" t="s">
+        <v>7</v>
+      </c>
+      <c r="C276" t="s">
+        <v>8</v>
+      </c>
+      <c r="D276" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>719</v>
+      </c>
+      <c r="B277" t="s">
+        <v>7</v>
+      </c>
+      <c r="C277" t="s">
+        <v>8</v>
+      </c>
+      <c r="D277" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>720</v>
+      </c>
+      <c r="B278" t="s">
+        <v>7</v>
+      </c>
+      <c r="C278" t="s">
+        <v>8</v>
+      </c>
+      <c r="D278" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>721</v>
+      </c>
+      <c r="B279" t="s">
+        <v>7</v>
+      </c>
+      <c r="C279" t="s">
+        <v>8</v>
+      </c>
+      <c r="D279" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>722</v>
+      </c>
+      <c r="B280" t="s">
+        <v>7</v>
+      </c>
+      <c r="C280" t="s">
+        <v>8</v>
+      </c>
+      <c r="D280" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>723</v>
+      </c>
+      <c r="B281" t="s">
+        <v>7</v>
+      </c>
+      <c r="C281" t="s">
+        <v>8</v>
+      </c>
+      <c r="D281" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>724</v>
+      </c>
+      <c r="B282" t="s">
+        <v>7</v>
+      </c>
+      <c r="C282" t="s">
+        <v>8</v>
+      </c>
+      <c r="D282" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>725</v>
+      </c>
+      <c r="B283" t="s">
+        <v>7</v>
+      </c>
+      <c r="C283" t="s">
+        <v>8</v>
+      </c>
+      <c r="D283" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>726</v>
+      </c>
+      <c r="B284" t="s">
+        <v>7</v>
+      </c>
+      <c r="C284" t="s">
+        <v>8</v>
+      </c>
+      <c r="D284" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>727</v>
+      </c>
+      <c r="B285" t="s">
+        <v>7</v>
+      </c>
+      <c r="C285" t="s">
+        <v>8</v>
+      </c>
+      <c r="D285" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>728</v>
+      </c>
+      <c r="B286" t="s">
+        <v>7</v>
+      </c>
+      <c r="C286" t="s">
+        <v>8</v>
+      </c>
+      <c r="D286" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>729</v>
+      </c>
+      <c r="B287" t="s">
+        <v>7</v>
+      </c>
+      <c r="C287" t="s">
+        <v>8</v>
+      </c>
+      <c r="D287" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>730</v>
+      </c>
+      <c r="B288" t="s">
+        <v>7</v>
+      </c>
+      <c r="C288" t="s">
+        <v>8</v>
+      </c>
+      <c r="D288" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>731</v>
+      </c>
+      <c r="B289" t="s">
+        <v>7</v>
+      </c>
+      <c r="C289" t="s">
+        <v>8</v>
+      </c>
+      <c r="D289" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>732</v>
+      </c>
+      <c r="B290" t="s">
+        <v>7</v>
+      </c>
+      <c r="C290" t="s">
+        <v>8</v>
+      </c>
+      <c r="D290" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>733</v>
+      </c>
+      <c r="B291" t="s">
+        <v>7</v>
+      </c>
+      <c r="C291" t="s">
+        <v>8</v>
+      </c>
+      <c r="D291" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>734</v>
+      </c>
+      <c r="B292" t="s">
+        <v>7</v>
+      </c>
+      <c r="C292" t="s">
+        <v>8</v>
+      </c>
+      <c r="D292" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>735</v>
+      </c>
+      <c r="B293" t="s">
+        <v>7</v>
+      </c>
+      <c r="C293" t="s">
+        <v>8</v>
+      </c>
+      <c r="D293" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>736</v>
+      </c>
+      <c r="B294" t="s">
+        <v>7</v>
+      </c>
+      <c r="C294" t="s">
+        <v>8</v>
+      </c>
+      <c r="D294" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>737</v>
+      </c>
+      <c r="B295" t="s">
+        <v>7</v>
+      </c>
+      <c r="C295" t="s">
+        <v>8</v>
+      </c>
+      <c r="D295" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>738</v>
+      </c>
+      <c r="B296" t="s">
+        <v>7</v>
+      </c>
+      <c r="C296" t="s">
+        <v>8</v>
+      </c>
+      <c r="D296" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>739</v>
+      </c>
+      <c r="B297" t="s">
+        <v>7</v>
+      </c>
+      <c r="C297" t="s">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>740</v>
+      </c>
+      <c r="B298" t="s">
+        <v>7</v>
+      </c>
+      <c r="C298" t="s">
+        <v>8</v>
+      </c>
+      <c r="D298" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>741</v>
+      </c>
+      <c r="B299" t="s">
+        <v>7</v>
+      </c>
+      <c r="C299" t="s">
+        <v>8</v>
+      </c>
+      <c r="D299" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>742</v>
+      </c>
+      <c r="B300" t="s">
+        <v>7</v>
+      </c>
+      <c r="C300" t="s">
+        <v>8</v>
+      </c>
+      <c r="D300" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>743</v>
+      </c>
+      <c r="B301" t="s">
+        <v>7</v>
+      </c>
+      <c r="C301" t="s">
+        <v>8</v>
+      </c>
+      <c r="D301" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>744</v>
+      </c>
+      <c r="B302" t="s">
+        <v>7</v>
+      </c>
+      <c r="C302" t="s">
+        <v>8</v>
+      </c>
+      <c r="D302" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>745</v>
+      </c>
+      <c r="B303" t="s">
+        <v>7</v>
+      </c>
+      <c r="C303" t="s">
+        <v>8</v>
+      </c>
+      <c r="D303" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>746</v>
+      </c>
+      <c r="B304" t="s">
+        <v>7</v>
+      </c>
+      <c r="C304" t="s">
+        <v>8</v>
+      </c>
+      <c r="D304" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>747</v>
+      </c>
+      <c r="B305" t="s">
+        <v>4</v>
+      </c>
+      <c r="C305" t="s">
+        <v>5</v>
+      </c>
+      <c r="D305" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>748</v>
+      </c>
+      <c r="B306" t="s">
+        <v>7</v>
+      </c>
+      <c r="C306" t="s">
+        <v>8</v>
+      </c>
+      <c r="D306" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>749</v>
+      </c>
+      <c r="B307" t="s">
+        <v>4</v>
+      </c>
+      <c r="C307" t="s">
+        <v>5</v>
+      </c>
+      <c r="D307" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>750</v>
+      </c>
+      <c r="B308" t="s">
+        <v>4</v>
+      </c>
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+      <c r="D308" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>751</v>
+      </c>
+      <c r="B309" t="s">
+        <v>4</v>
+      </c>
+      <c r="C309" t="s">
+        <v>5</v>
+      </c>
+      <c r="D309" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>752</v>
+      </c>
+      <c r="B310" t="s">
+        <v>4</v>
+      </c>
+      <c r="C310" t="s">
+        <v>5</v>
+      </c>
+      <c r="D310" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>753</v>
+      </c>
+      <c r="B311" t="s">
+        <v>4</v>
+      </c>
+      <c r="C311" t="s">
+        <v>5</v>
+      </c>
+      <c r="D311" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>754</v>
+      </c>
+      <c r="B312" t="s">
+        <v>4</v>
+      </c>
+      <c r="C312" t="s">
+        <v>5</v>
+      </c>
+      <c r="D312" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>755</v>
+      </c>
+      <c r="B313" t="s">
+        <v>4</v>
+      </c>
+      <c r="C313" t="s">
+        <v>5</v>
+      </c>
+      <c r="D313" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>756</v>
+      </c>
+      <c r="B314" t="s">
+        <v>4</v>
+      </c>
+      <c r="C314" t="s">
+        <v>5</v>
+      </c>
+      <c r="D314" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>757</v>
+      </c>
+      <c r="B315" t="s">
+        <v>4</v>
+      </c>
+      <c r="C315" t="s">
+        <v>5</v>
+      </c>
+      <c r="D315" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>758</v>
+      </c>
+      <c r="B316" t="s">
+        <v>4</v>
+      </c>
+      <c r="C316" t="s">
+        <v>5</v>
+      </c>
+      <c r="D316" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>759</v>
+      </c>
+      <c r="B317" t="s">
+        <v>4</v>
+      </c>
+      <c r="C317" t="s">
+        <v>5</v>
+      </c>
+      <c r="D317" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>760</v>
+      </c>
+      <c r="B318" t="s">
+        <v>4</v>
+      </c>
+      <c r="C318" t="s">
+        <v>5</v>
+      </c>
+      <c r="D318" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>761</v>
+      </c>
+      <c r="B319" t="s">
+        <v>4</v>
+      </c>
+      <c r="C319" t="s">
+        <v>5</v>
+      </c>
+      <c r="D319" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>762</v>
+      </c>
+      <c r="B320" t="s">
+        <v>4</v>
+      </c>
+      <c r="C320" t="s">
+        <v>5</v>
+      </c>
+      <c r="D320" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>763</v>
+      </c>
+      <c r="B321" t="s">
+        <v>7</v>
+      </c>
+      <c r="C321" t="s">
+        <v>8</v>
+      </c>
+      <c r="D321" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>764</v>
+      </c>
+      <c r="B322" t="s">
+        <v>4</v>
+      </c>
+      <c r="C322" t="s">
+        <v>5</v>
+      </c>
+      <c r="D322" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>765</v>
+      </c>
+      <c r="B323" t="s">
+        <v>4</v>
+      </c>
+      <c r="C323" t="s">
+        <v>5</v>
+      </c>
+      <c r="D323" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>766</v>
+      </c>
+      <c r="B324" t="s">
+        <v>4</v>
+      </c>
+      <c r="C324" t="s">
+        <v>5</v>
+      </c>
+      <c r="D324" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>767</v>
+      </c>
+      <c r="B325" t="s">
+        <v>4</v>
+      </c>
+      <c r="C325" t="s">
+        <v>5</v>
+      </c>
+      <c r="D325" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>768</v>
+      </c>
+      <c r="B326" t="s">
+        <v>7</v>
+      </c>
+      <c r="C326" t="s">
+        <v>8</v>
+      </c>
+      <c r="D326" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>769</v>
+      </c>
+      <c r="B327" t="s">
+        <v>4</v>
+      </c>
+      <c r="C327" t="s">
+        <v>5</v>
+      </c>
+      <c r="D327" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>770</v>
+      </c>
+      <c r="B328" t="s">
+        <v>7</v>
+      </c>
+      <c r="C328" t="s">
+        <v>8</v>
+      </c>
+      <c r="D328" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>771</v>
+      </c>
+      <c r="B329" t="s">
+        <v>4</v>
+      </c>
+      <c r="C329" t="s">
+        <v>5</v>
+      </c>
+      <c r="D329" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>772</v>
+      </c>
+      <c r="B330" t="s">
+        <v>4</v>
+      </c>
+      <c r="C330" t="s">
+        <v>5</v>
+      </c>
+      <c r="D330" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>773</v>
+      </c>
+      <c r="B331" t="s">
+        <v>4</v>
+      </c>
+      <c r="C331" t="s">
+        <v>5</v>
+      </c>
+      <c r="D331" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>774</v>
+      </c>
+      <c r="B332" t="s">
+        <v>4</v>
+      </c>
+      <c r="C332" t="s">
+        <v>5</v>
+      </c>
+      <c r="D332" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>775</v>
+      </c>
+      <c r="B333" t="s">
+        <v>4</v>
+      </c>
+      <c r="C333" t="s">
+        <v>5</v>
+      </c>
+      <c r="D333" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>776</v>
+      </c>
+      <c r="B334" t="s">
+        <v>4</v>
+      </c>
+      <c r="C334" t="s">
+        <v>5</v>
+      </c>
+      <c r="D334" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>777</v>
+      </c>
+      <c r="B335" t="s">
+        <v>4</v>
+      </c>
+      <c r="C335" t="s">
+        <v>5</v>
+      </c>
+      <c r="D335" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>778</v>
+      </c>
+      <c r="B336" t="s">
+        <v>4</v>
+      </c>
+      <c r="C336" t="s">
+        <v>5</v>
+      </c>
+      <c r="D336" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>779</v>
+      </c>
+      <c r="B337" t="s">
+        <v>4</v>
+      </c>
+      <c r="C337" t="s">
+        <v>5</v>
+      </c>
+      <c r="D337" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>780</v>
+      </c>
+      <c r="B338" t="s">
+        <v>4</v>
+      </c>
+      <c r="C338" t="s">
+        <v>5</v>
+      </c>
+      <c r="D338" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>781</v>
+      </c>
+      <c r="B339" t="s">
+        <v>4</v>
+      </c>
+      <c r="C339" t="s">
+        <v>5</v>
+      </c>
+      <c r="D339" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>782</v>
+      </c>
+      <c r="B340" t="s">
+        <v>4</v>
+      </c>
+      <c r="C340" t="s">
+        <v>5</v>
+      </c>
+      <c r="D340" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>783</v>
+      </c>
+      <c r="B341" t="s">
+        <v>4</v>
+      </c>
+      <c r="C341" t="s">
+        <v>5</v>
+      </c>
+      <c r="D341" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>784</v>
+      </c>
+      <c r="B342" t="s">
+        <v>4</v>
+      </c>
+      <c r="C342" t="s">
+        <v>5</v>
+      </c>
+      <c r="D342" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>785</v>
+      </c>
+      <c r="B343" t="s">
+        <v>4</v>
+      </c>
+      <c r="C343" t="s">
+        <v>5</v>
+      </c>
+      <c r="D343" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>786</v>
+      </c>
+      <c r="B344" t="s">
+        <v>4</v>
+      </c>
+      <c r="C344" t="s">
+        <v>5</v>
+      </c>
+      <c r="D344" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>787</v>
+      </c>
+      <c r="B345" t="s">
+        <v>4</v>
+      </c>
+      <c r="C345" t="s">
+        <v>5</v>
+      </c>
+      <c r="D345" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>788</v>
+      </c>
+      <c r="B346" t="s">
+        <v>4</v>
+      </c>
+      <c r="C346" t="s">
+        <v>5</v>
+      </c>
+      <c r="D346" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>789</v>
+      </c>
+      <c r="B347" t="s">
+        <v>4</v>
+      </c>
+      <c r="C347" t="s">
+        <v>5</v>
+      </c>
+      <c r="D347" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>790</v>
+      </c>
+      <c r="B348" t="s">
+        <v>4</v>
+      </c>
+      <c r="C348" t="s">
+        <v>5</v>
+      </c>
+      <c r="D348" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>791</v>
+      </c>
+      <c r="B349" t="s">
+        <v>7</v>
+      </c>
+      <c r="C349" t="s">
+        <v>8</v>
+      </c>
+      <c r="D349" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>792</v>
+      </c>
+      <c r="B350" t="s">
+        <v>4</v>
+      </c>
+      <c r="C350" t="s">
+        <v>5</v>
+      </c>
+      <c r="D350" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>793</v>
+      </c>
+      <c r="B351" t="s">
+        <v>7</v>
+      </c>
+      <c r="C351" t="s">
+        <v>8</v>
+      </c>
+      <c r="D351" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>794</v>
+      </c>
+      <c r="B352" t="s">
+        <v>4</v>
+      </c>
+      <c r="C352" t="s">
+        <v>5</v>
+      </c>
+      <c r="D352" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>795</v>
+      </c>
+      <c r="B353" t="s">
+        <v>4</v>
+      </c>
+      <c r="C353" t="s">
+        <v>5</v>
+      </c>
+      <c r="D353" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>796</v>
+      </c>
+      <c r="B354" t="s">
+        <v>4</v>
+      </c>
+      <c r="C354" t="s">
+        <v>5</v>
+      </c>
+      <c r="D354" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>797</v>
+      </c>
+      <c r="B355" t="s">
+        <v>4</v>
+      </c>
+      <c r="C355" t="s">
+        <v>5</v>
+      </c>
+      <c r="D355" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>798</v>
+      </c>
+      <c r="B356" t="s">
+        <v>4</v>
+      </c>
+      <c r="C356" t="s">
+        <v>5</v>
+      </c>
+      <c r="D356" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>799</v>
+      </c>
+      <c r="B357" t="s">
+        <v>7</v>
+      </c>
+      <c r="C357" t="s">
+        <v>8</v>
+      </c>
+      <c r="D357" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>800</v>
+      </c>
+      <c r="B358" t="s">
+        <v>4</v>
+      </c>
+      <c r="C358" t="s">
+        <v>5</v>
+      </c>
+      <c r="D358" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>801</v>
+      </c>
+      <c r="B359" t="s">
+        <v>4</v>
+      </c>
+      <c r="C359" t="s">
+        <v>5</v>
+      </c>
+      <c r="D359" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>802</v>
+      </c>
+      <c r="B360" t="s">
+        <v>4</v>
+      </c>
+      <c r="C360" t="s">
+        <v>5</v>
+      </c>
+      <c r="D360" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>803</v>
+      </c>
+      <c r="B361" t="s">
+        <v>4</v>
+      </c>
+      <c r="C361" t="s">
+        <v>5</v>
+      </c>
+      <c r="D361" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>804</v>
+      </c>
+      <c r="B362" t="s">
+        <v>4</v>
+      </c>
+      <c r="C362" t="s">
+        <v>5</v>
+      </c>
+      <c r="D362" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>805</v>
+      </c>
+      <c r="B363" t="s">
+        <v>4</v>
+      </c>
+      <c r="C363" t="s">
+        <v>5</v>
+      </c>
+      <c r="D363" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>806</v>
+      </c>
+      <c r="B364" t="s">
+        <v>4</v>
+      </c>
+      <c r="C364" t="s">
+        <v>5</v>
+      </c>
+      <c r="D364" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>807</v>
+      </c>
+      <c r="B365" t="s">
+        <v>4</v>
+      </c>
+      <c r="C365" t="s">
+        <v>5</v>
+      </c>
+      <c r="D365" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>808</v>
+      </c>
+      <c r="B366" t="s">
+        <v>4</v>
+      </c>
+      <c r="C366" t="s">
+        <v>5</v>
+      </c>
+      <c r="D366" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>809</v>
+      </c>
+      <c r="B367" t="s">
+        <v>4</v>
+      </c>
+      <c r="C367" t="s">
+        <v>5</v>
+      </c>
+      <c r="D367" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>810</v>
+      </c>
+      <c r="B368" t="s">
+        <v>4</v>
+      </c>
+      <c r="C368" t="s">
+        <v>5</v>
+      </c>
+      <c r="D368" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>811</v>
+      </c>
+      <c r="B369" t="s">
+        <v>4</v>
+      </c>
+      <c r="C369" t="s">
+        <v>5</v>
+      </c>
+      <c r="D369" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>812</v>
+      </c>
+      <c r="B370" t="s">
+        <v>4</v>
+      </c>
+      <c r="C370" t="s">
+        <v>5</v>
+      </c>
+      <c r="D370" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>813</v>
+      </c>
+      <c r="B371" t="s">
+        <v>7</v>
+      </c>
+      <c r="C371" t="s">
+        <v>8</v>
+      </c>
+      <c r="D371" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>814</v>
+      </c>
+      <c r="B372" t="s">
+        <v>4</v>
+      </c>
+      <c r="C372" t="s">
+        <v>5</v>
+      </c>
+      <c r="D372" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>815</v>
+      </c>
+      <c r="B373" t="s">
+        <v>4</v>
+      </c>
+      <c r="C373" t="s">
+        <v>5</v>
+      </c>
+      <c r="D373" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>816</v>
+      </c>
+      <c r="B374" t="s">
+        <v>4</v>
+      </c>
+      <c r="C374" t="s">
+        <v>5</v>
+      </c>
+      <c r="D374" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>817</v>
+      </c>
+      <c r="B375" t="s">
+        <v>4</v>
+      </c>
+      <c r="C375" t="s">
+        <v>5</v>
+      </c>
+      <c r="D375" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>818</v>
+      </c>
+      <c r="B376" t="s">
+        <v>7</v>
+      </c>
+      <c r="C376" t="s">
+        <v>8</v>
+      </c>
+      <c r="D376" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>819</v>
+      </c>
+      <c r="B377" t="s">
+        <v>4</v>
+      </c>
+      <c r="C377" t="s">
+        <v>5</v>
+      </c>
+      <c r="D377" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>820</v>
+      </c>
+      <c r="B378" t="s">
+        <v>7</v>
+      </c>
+      <c r="C378" t="s">
+        <v>8</v>
+      </c>
+      <c r="D378" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>821</v>
+      </c>
+      <c r="B379" t="s">
+        <v>4</v>
+      </c>
+      <c r="C379" t="s">
+        <v>5</v>
+      </c>
+      <c r="D379" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>822</v>
+      </c>
+      <c r="B380" t="s">
+        <v>4</v>
+      </c>
+      <c r="C380" t="s">
+        <v>5</v>
+      </c>
+      <c r="D380" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>823</v>
+      </c>
+      <c r="B381" t="s">
+        <v>4</v>
+      </c>
+      <c r="C381" t="s">
+        <v>5</v>
+      </c>
+      <c r="D381" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>824</v>
+      </c>
+      <c r="B382" t="s">
+        <v>4</v>
+      </c>
+      <c r="C382" t="s">
+        <v>5</v>
+      </c>
+      <c r="D382" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>825</v>
+      </c>
+      <c r="B383" t="s">
+        <v>4</v>
+      </c>
+      <c r="C383" t="s">
+        <v>5</v>
+      </c>
+      <c r="D383" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>826</v>
+      </c>
+      <c r="B384" t="s">
+        <v>4</v>
+      </c>
+      <c r="C384" t="s">
+        <v>5</v>
+      </c>
+      <c r="D384" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>827</v>
+      </c>
+      <c r="B385" t="s">
+        <v>4</v>
+      </c>
+      <c r="C385" t="s">
+        <v>5</v>
+      </c>
+      <c r="D385" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>828</v>
+      </c>
+      <c r="B386" t="s">
+        <v>4</v>
+      </c>
+      <c r="C386" t="s">
+        <v>5</v>
+      </c>
+      <c r="D386" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>829</v>
+      </c>
+      <c r="B387" t="s">
+        <v>4</v>
+      </c>
+      <c r="C387" t="s">
+        <v>5</v>
+      </c>
+      <c r="D387" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>830</v>
+      </c>
+      <c r="B388" t="s">
+        <v>4</v>
+      </c>
+      <c r="C388" t="s">
+        <v>5</v>
+      </c>
+      <c r="D388" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>831</v>
+      </c>
+      <c r="B389" t="s">
+        <v>4</v>
+      </c>
+      <c r="C389" t="s">
+        <v>5</v>
+      </c>
+      <c r="D389" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>832</v>
+      </c>
+      <c r="B390" t="s">
+        <v>4</v>
+      </c>
+      <c r="C390" t="s">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>833</v>
+      </c>
+      <c r="B391" t="s">
+        <v>4</v>
+      </c>
+      <c r="C391" t="s">
+        <v>5</v>
+      </c>
+      <c r="D391" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>834</v>
+      </c>
+      <c r="B392" t="s">
+        <v>4</v>
+      </c>
+      <c r="C392" t="s">
+        <v>5</v>
+      </c>
+      <c r="D392" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>835</v>
+      </c>
+      <c r="B393" t="s">
+        <v>4</v>
+      </c>
+      <c r="C393" t="s">
+        <v>5</v>
+      </c>
+      <c r="D393" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>836</v>
+      </c>
+      <c r="B394" t="s">
+        <v>4</v>
+      </c>
+      <c r="C394" t="s">
+        <v>5</v>
+      </c>
+      <c r="D394" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>837</v>
+      </c>
+      <c r="B395" t="s">
+        <v>7</v>
+      </c>
+      <c r="C395" t="s">
+        <v>8</v>
+      </c>
+      <c r="D395" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>838</v>
+      </c>
+      <c r="B396" t="s">
+        <v>4</v>
+      </c>
+      <c r="C396" t="s">
+        <v>5</v>
+      </c>
+      <c r="D396" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>839</v>
+      </c>
+      <c r="B397" t="s">
+        <v>7</v>
+      </c>
+      <c r="C397" t="s">
+        <v>8</v>
+      </c>
+      <c r="D397" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>840</v>
+      </c>
+      <c r="B398" t="s">
+        <v>4</v>
+      </c>
+      <c r="C398" t="s">
+        <v>5</v>
+      </c>
+      <c r="D398" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>841</v>
+      </c>
+      <c r="B399" t="s">
+        <v>4</v>
+      </c>
+      <c r="C399" t="s">
+        <v>5</v>
+      </c>
+      <c r="D399" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>842</v>
+      </c>
+      <c r="B400" t="s">
+        <v>4</v>
+      </c>
+      <c r="C400" t="s">
+        <v>5</v>
+      </c>
+      <c r="D400" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>843</v>
+      </c>
+      <c r="B401" t="s">
+        <v>4</v>
+      </c>
+      <c r="C401" t="s">
+        <v>5</v>
+      </c>
+      <c r="D401" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>844</v>
+      </c>
+      <c r="B402" t="s">
+        <v>7</v>
+      </c>
+      <c r="C402" t="s">
+        <v>8</v>
+      </c>
+      <c r="D402" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>845</v>
+      </c>
+      <c r="B403" t="s">
+        <v>7</v>
+      </c>
+      <c r="C403" t="s">
+        <v>8</v>
+      </c>
+      <c r="D403" t="s">
+        <v>409</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/apps/backend/excel-data/holidaystudentsub_library_migration.xlsx
+++ b/apps/backend/excel-data/holidaystudentsub_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="553">
   <si>
     <t>legacy_id</t>
   </si>
@@ -122,6 +122,1554 @@
   </si>
   <si>
     <t>2026-06-20T06:43:15.952Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:36:59.390Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:00.417Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:01.435Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:02.423Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:03.377Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:04.263Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:05.189Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:06.095Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:06.939Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:07.888Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:08.742Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:09.674Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:10.646Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:11.568Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:12.431Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:13.343Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:14.185Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:15.353Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:16.278Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:17.521Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:18.850Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:20.142Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:21.260Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:22.467Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:23.662Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:24.884Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:26.043Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:27.351Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:29.086Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:30.277Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:31.502Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:32.662Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:33.825Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:34.840Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:36.356Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:37.724Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:38.843Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:40.050Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:41.098Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:42.533Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:43.565Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:44.879Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:46.171Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:47.721Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:49.328Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:50.676Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:51.931Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:53.262Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:54.572Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:55.956Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:57.345Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:58.587Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:37:59.942Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:01.788Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:03.104Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:04.435Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:05.756Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:07.107Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:08.430Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:09.850Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:11.568Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:12.540Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:13.823Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:14.782Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:15.922Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:17.149Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:18.360Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:19.535Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:20.722Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:21.622Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:22.762Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:23.940Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:25.188Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:26.431Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:27.593Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:28.817Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:30.724Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:32.294Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:33.671Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:34.945Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:36.248Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:37.937Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:39.269Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:40.202Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:41.512Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:42.852Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:44.381Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:45.607Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:46.610Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:48.236Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:49.378Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:51.418Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:53.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:54.698Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:56.432Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:38:58.423Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:00.186Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:01.827Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:04.864Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:06.499Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:07.985Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:09.839Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:11.600Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:13.648Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:15.780Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:17.836Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:19.291Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:20.337Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:22.006Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:23.517Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:25.128Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:26.654Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:28.017Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:29.442Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:30.687Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:31.831Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:32.828Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:33.974Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:35.119Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:36.305Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:37.640Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:38.847Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:40.049Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:41.074Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:42.145Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:43.325Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:45.053Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:46.551Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:47.811Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:49.049Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:50.666Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:52.366Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:53.957Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:55.738Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:57.448Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:39:59.480Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:01.695Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:03.742Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:05.367Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:07.511Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:09.368Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:11.014Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:13.221Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:14.736Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:18.127Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:19.778Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:21.208Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:22.455Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:23.963Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:25.450Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:26.815Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:28.400Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:29.584Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:30.950Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:32.485Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:34.316Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:35.954Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:37.444Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:38.812Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:40.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:41.419Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:42.745Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:43.982Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:45.317Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:46.585Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:47.745Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:49.027Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:50.305Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:51.675Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:53.620Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:55.543Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:56.956Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:58.784Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:40:59.969Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:02.316Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:03.597Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:05.146Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:06.506Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:08.026Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:09.633Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:11.034Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:12.268Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:14.167Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:16.477Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:17.969Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:19.536Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:21.150Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:22.784Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:24.508Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:26.042Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:27.293Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:28.635Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:29.859Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:31.186Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:32.514Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:33.399Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:34.676Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:36.009Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:37.175Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:41:38.423Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:42:56.944Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:42:58.225Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:42:59.285Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:00.269Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:01.248Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:02.197Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:03.205Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:04.269Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:05.273Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:06.266Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:07.287Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:08.355Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:09.689Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:10.874Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:11.833Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:12.966Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:13.917Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:14.909Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:15.938Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:16.937Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:17.985Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:19.112Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:20.080Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:21.060Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:22.181Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:23.200Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:24.225Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:25.257Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:26.284Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:27.308Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:28.330Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:29.457Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:30.491Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:31.478Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:32.597Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:33.667Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:34.670Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:35.696Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:36.733Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:37.748Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:38.658Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:39.590Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:40.597Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:42.661Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:43.905Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:45.024Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:46.152Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:47.236Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:48.393Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:49.838Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:51.228Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:52.263Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:53.273Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:54.301Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:55.376Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:56.926Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:58.436Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:43:59.672Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:01.400Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:02.947Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:04.027Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:05.319Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:06.606Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:07.969Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:09.097Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:10.294Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:11.500Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:12.682Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:15.937Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:20.545Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:23.427Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:25.438Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:27.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:29.237Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:31.276Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:33.386Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:35.548Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:38.079Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:40.314Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:42.244Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:44.191Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:46.363Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:48.527Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:50.790Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:53.554Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:56.065Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:57.750Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:44:59.595Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:00.866Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:02.735Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:04.094Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:06.325Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:08.597Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:10.245Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:12.107Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:15.278Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:18.127Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:20.433Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:22.704Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:24.417Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:26.686Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:28.722Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:30.689Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:32.352Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:34.457Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:36.652Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:38.488Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:40.403Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:42.662Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:45.042Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:48.973Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:52.310Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:53.993Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:55.410Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:56.814Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:45:58.810Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:01.343Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:03.430Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:05.121Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:06.620Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:08.769Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:10.956Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:12.853Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:17.440Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:20.179Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:24.200Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:28.376Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:32.086Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:33.870Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:36.751Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:38.888Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:41.158Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:43.232Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:45.750Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:48.201Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:50.285Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:52.242Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:53.927Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:55.567Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:57.263Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:46:58.878Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:00.309Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:01.840Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:03.070Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:04.810Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:06.179Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:07.598Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:10.191Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:11.666Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:13.646Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:14.944Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:17.358Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:19.141Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:20.619Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:22.111Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:23.966Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:25.989Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:27.768Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:29.882Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:31.899Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:33.546Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:35.473Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:37.236Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:39.450Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:40.953Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:42.364Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:43.886Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:45.380Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:47.069Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:48.637Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:50.181Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:51.402Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:52.840Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:53.959Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:55.485Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:56.946Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:47:59.104Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:00.845Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:02.338Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:03.593Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:04.921Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:06.356Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:09.735Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:12.979Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:15.204Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:17.650Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:25.422Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:27.445Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:29.218Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:31.397Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:33.584Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:35.184Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:37.094Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:38.724Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:40.820Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:42.859Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:44.933Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:46.952Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:48.581Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:50.940Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:52.632Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:55.504Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:58.130Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:48:59.699Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:01.301Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:02.901Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:04.419Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:05.861Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:07.510Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:09.148Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:12.118Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:14.962Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:17.129Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:18.748Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:20.372Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:21.878Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:23.764Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:25.110Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:26.577Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:27.768Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:29.171Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:31.077Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:32.986Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:34.969Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:37.302Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:38.621Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:39.647Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:40.687Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:41.753Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:42.775Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:43.841Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:44.947Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:46.061Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:47.092Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:48.080Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:49.170Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:50.298Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:51.487Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:52.538Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:53.910Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:55.184Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:56.570Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:57.732Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:49:58.850Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:00.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:01.363Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:02.604Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:04.435Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:05.802Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:07.872Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:09.816Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:11.194Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:13.088Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:14.544Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:15.915Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:18.099Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:20.225Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:21.914Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:23.607Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:25.372Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:26.971Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:28.850Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:30.744Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:32.422Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:34.005Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:35.702Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:37.352Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:39.061Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:40.791Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:42.622Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:44.288Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:46.198Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:47.395Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:48.777Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:50.238Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:51.656Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:53.200Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:54.331Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:55.994Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:57.626Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:50:59.307Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:00.739Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:02.523Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:04.228Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:05.759Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:07.346Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:08.839Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:10.355Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:11.816Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:13.267Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:14.836Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:16.374Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:18.462Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:21.486Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:22.983Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:24.451Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:25.821Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:27.278Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:28.684Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:30.048Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:31.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:32.509Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:33.681Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:35.144Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:36.401Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:37.723Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:39.051Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:40.464Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:41.417Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:42.817Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:44.180Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:45.803Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:47.186Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:49.370Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:50.735Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:52.367Z</t>
   </si>
 </sst>
 </file>
@@ -502,7 +2050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D546"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -925,6 +2473,7230 @@
         <v>36</v>
       </c>
     </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>10</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>17</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>20</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>21</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>22</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>23</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>24</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>26</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>28</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>29</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>31</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>32</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>33</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>34</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>35</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>38</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>39</v>
+      </c>
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>40</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>41</v>
+      </c>
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>42</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>43</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>44</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>45</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>46</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>47</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>48</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>49</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>50</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>51</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>52</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>53</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>54</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>55</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>56</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>57</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>58</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>59</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>60</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>61</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>62</v>
+      </c>
+      <c r="B92" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>63</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>64</v>
+      </c>
+      <c r="B94" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>65</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>66</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>67</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>68</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>69</v>
+      </c>
+      <c r="B99" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>70</v>
+      </c>
+      <c r="B100" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>71</v>
+      </c>
+      <c r="B101" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>72</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>73</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>74</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+      <c r="D104" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>75</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+      <c r="D105" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>76</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>77</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>78</v>
+      </c>
+      <c r="B108" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>79</v>
+      </c>
+      <c r="B109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>80</v>
+      </c>
+      <c r="B110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>81</v>
+      </c>
+      <c r="B111" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>82</v>
+      </c>
+      <c r="B112" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>83</v>
+      </c>
+      <c r="B113" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>84</v>
+      </c>
+      <c r="B114" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>85</v>
+      </c>
+      <c r="B115" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>86</v>
+      </c>
+      <c r="B116" t="s">
+        <v>4</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>87</v>
+      </c>
+      <c r="B117" t="s">
+        <v>4</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>88</v>
+      </c>
+      <c r="B118" t="s">
+        <v>4</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>89</v>
+      </c>
+      <c r="B119" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>90</v>
+      </c>
+      <c r="B120" t="s">
+        <v>4</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>91</v>
+      </c>
+      <c r="B121" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>92</v>
+      </c>
+      <c r="B122" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>93</v>
+      </c>
+      <c r="B123" t="s">
+        <v>4</v>
+      </c>
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>94</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4</v>
+      </c>
+      <c r="C124" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>95</v>
+      </c>
+      <c r="B125" t="s">
+        <v>4</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>96</v>
+      </c>
+      <c r="B126" t="s">
+        <v>4</v>
+      </c>
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>97</v>
+      </c>
+      <c r="B127" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>98</v>
+      </c>
+      <c r="B128" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>99</v>
+      </c>
+      <c r="B129" t="s">
+        <v>4</v>
+      </c>
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>100</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>101</v>
+      </c>
+      <c r="B131" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>102</v>
+      </c>
+      <c r="B132" t="s">
+        <v>4</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>103</v>
+      </c>
+      <c r="B133" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>104</v>
+      </c>
+      <c r="B134" t="s">
+        <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>105</v>
+      </c>
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>106</v>
+      </c>
+      <c r="B136" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>107</v>
+      </c>
+      <c r="B137" t="s">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>5</v>
+      </c>
+      <c r="D137" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>108</v>
+      </c>
+      <c r="B138" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" t="s">
+        <v>8</v>
+      </c>
+      <c r="D138" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>109</v>
+      </c>
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" t="s">
+        <v>5</v>
+      </c>
+      <c r="D139" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>110</v>
+      </c>
+      <c r="B140" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>111</v>
+      </c>
+      <c r="B141" t="s">
+        <v>4</v>
+      </c>
+      <c r="C141" t="s">
+        <v>5</v>
+      </c>
+      <c r="D141" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>112</v>
+      </c>
+      <c r="B142" t="s">
+        <v>4</v>
+      </c>
+      <c r="C142" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>113</v>
+      </c>
+      <c r="B143" t="s">
+        <v>4</v>
+      </c>
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>114</v>
+      </c>
+      <c r="B144" t="s">
+        <v>4</v>
+      </c>
+      <c r="C144" t="s">
+        <v>5</v>
+      </c>
+      <c r="D144" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>457</v>
+      </c>
+      <c r="B145" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" t="s">
+        <v>8</v>
+      </c>
+      <c r="D145" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>458</v>
+      </c>
+      <c r="B146" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" t="s">
+        <v>8</v>
+      </c>
+      <c r="D146" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>459</v>
+      </c>
+      <c r="B147" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>460</v>
+      </c>
+      <c r="B148" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>461</v>
+      </c>
+      <c r="B149" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>462</v>
+      </c>
+      <c r="B150" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>463</v>
+      </c>
+      <c r="B151" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>464</v>
+      </c>
+      <c r="B152" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>465</v>
+      </c>
+      <c r="B153" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>466</v>
+      </c>
+      <c r="B154" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>467</v>
+      </c>
+      <c r="B155" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>468</v>
+      </c>
+      <c r="B156" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>469</v>
+      </c>
+      <c r="B157" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>470</v>
+      </c>
+      <c r="B158" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>471</v>
+      </c>
+      <c r="B159" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>472</v>
+      </c>
+      <c r="B160" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>473</v>
+      </c>
+      <c r="B161" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>474</v>
+      </c>
+      <c r="B162" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>475</v>
+      </c>
+      <c r="B163" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>476</v>
+      </c>
+      <c r="B164" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>477</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>478</v>
+      </c>
+      <c r="B166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>479</v>
+      </c>
+      <c r="B167" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>480</v>
+      </c>
+      <c r="B168" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>481</v>
+      </c>
+      <c r="B169" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>482</v>
+      </c>
+      <c r="B170" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>483</v>
+      </c>
+      <c r="B171" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>484</v>
+      </c>
+      <c r="B172" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>485</v>
+      </c>
+      <c r="B173" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>486</v>
+      </c>
+      <c r="B174" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>487</v>
+      </c>
+      <c r="B175" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>488</v>
+      </c>
+      <c r="B176" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>490</v>
+      </c>
+      <c r="B177" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>505</v>
+      </c>
+      <c r="B178" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" t="s">
+        <v>8</v>
+      </c>
+      <c r="D178" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>508</v>
+      </c>
+      <c r="B179" t="s">
+        <v>4</v>
+      </c>
+      <c r="C179" t="s">
+        <v>5</v>
+      </c>
+      <c r="D179" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>509</v>
+      </c>
+      <c r="B180" t="s">
+        <v>4</v>
+      </c>
+      <c r="C180" t="s">
+        <v>5</v>
+      </c>
+      <c r="D180" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>510</v>
+      </c>
+      <c r="B181" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>511</v>
+      </c>
+      <c r="B182" t="s">
+        <v>4</v>
+      </c>
+      <c r="C182" t="s">
+        <v>5</v>
+      </c>
+      <c r="D182" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>512</v>
+      </c>
+      <c r="B183" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" t="s">
+        <v>8</v>
+      </c>
+      <c r="D183" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>513</v>
+      </c>
+      <c r="B184" t="s">
+        <v>4</v>
+      </c>
+      <c r="C184" t="s">
+        <v>5</v>
+      </c>
+      <c r="D184" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>514</v>
+      </c>
+      <c r="B185" t="s">
+        <v>4</v>
+      </c>
+      <c r="C185" t="s">
+        <v>5</v>
+      </c>
+      <c r="D185" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>515</v>
+      </c>
+      <c r="B186" t="s">
+        <v>4</v>
+      </c>
+      <c r="C186" t="s">
+        <v>5</v>
+      </c>
+      <c r="D186" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>516</v>
+      </c>
+      <c r="B187" t="s">
+        <v>4</v>
+      </c>
+      <c r="C187" t="s">
+        <v>5</v>
+      </c>
+      <c r="D187" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>517</v>
+      </c>
+      <c r="B188" t="s">
+        <v>4</v>
+      </c>
+      <c r="C188" t="s">
+        <v>5</v>
+      </c>
+      <c r="D188" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>518</v>
+      </c>
+      <c r="B189" t="s">
+        <v>4</v>
+      </c>
+      <c r="C189" t="s">
+        <v>5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>519</v>
+      </c>
+      <c r="B190" t="s">
+        <v>4</v>
+      </c>
+      <c r="C190" t="s">
+        <v>5</v>
+      </c>
+      <c r="D190" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>520</v>
+      </c>
+      <c r="B191" t="s">
+        <v>4</v>
+      </c>
+      <c r="C191" t="s">
+        <v>5</v>
+      </c>
+      <c r="D191" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>521</v>
+      </c>
+      <c r="B192" t="s">
+        <v>4</v>
+      </c>
+      <c r="C192" t="s">
+        <v>5</v>
+      </c>
+      <c r="D192" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>522</v>
+      </c>
+      <c r="B193" t="s">
+        <v>4</v>
+      </c>
+      <c r="C193" t="s">
+        <v>5</v>
+      </c>
+      <c r="D193" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>523</v>
+      </c>
+      <c r="B194" t="s">
+        <v>4</v>
+      </c>
+      <c r="C194" t="s">
+        <v>5</v>
+      </c>
+      <c r="D194" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>524</v>
+      </c>
+      <c r="B195" t="s">
+        <v>4</v>
+      </c>
+      <c r="C195" t="s">
+        <v>5</v>
+      </c>
+      <c r="D195" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>525</v>
+      </c>
+      <c r="B196" t="s">
+        <v>4</v>
+      </c>
+      <c r="C196" t="s">
+        <v>5</v>
+      </c>
+      <c r="D196" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>526</v>
+      </c>
+      <c r="B197" t="s">
+        <v>4</v>
+      </c>
+      <c r="C197" t="s">
+        <v>5</v>
+      </c>
+      <c r="D197" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>527</v>
+      </c>
+      <c r="B198" t="s">
+        <v>4</v>
+      </c>
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>528</v>
+      </c>
+      <c r="B199" t="s">
+        <v>4</v>
+      </c>
+      <c r="C199" t="s">
+        <v>5</v>
+      </c>
+      <c r="D199" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>529</v>
+      </c>
+      <c r="B200" t="s">
+        <v>4</v>
+      </c>
+      <c r="C200" t="s">
+        <v>5</v>
+      </c>
+      <c r="D200" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>530</v>
+      </c>
+      <c r="B201" t="s">
+        <v>4</v>
+      </c>
+      <c r="C201" t="s">
+        <v>5</v>
+      </c>
+      <c r="D201" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>531</v>
+      </c>
+      <c r="B202" t="s">
+        <v>4</v>
+      </c>
+      <c r="C202" t="s">
+        <v>5</v>
+      </c>
+      <c r="D202" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>532</v>
+      </c>
+      <c r="B203" t="s">
+        <v>4</v>
+      </c>
+      <c r="C203" t="s">
+        <v>5</v>
+      </c>
+      <c r="D203" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>533</v>
+      </c>
+      <c r="B204" t="s">
+        <v>7</v>
+      </c>
+      <c r="C204" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>534</v>
+      </c>
+      <c r="B205" t="s">
+        <v>4</v>
+      </c>
+      <c r="C205" t="s">
+        <v>5</v>
+      </c>
+      <c r="D205" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>535</v>
+      </c>
+      <c r="B206" t="s">
+        <v>7</v>
+      </c>
+      <c r="C206" t="s">
+        <v>8</v>
+      </c>
+      <c r="D206" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>536</v>
+      </c>
+      <c r="B207" t="s">
+        <v>4</v>
+      </c>
+      <c r="C207" t="s">
+        <v>5</v>
+      </c>
+      <c r="D207" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>537</v>
+      </c>
+      <c r="B208" t="s">
+        <v>4</v>
+      </c>
+      <c r="C208" t="s">
+        <v>5</v>
+      </c>
+      <c r="D208" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>538</v>
+      </c>
+      <c r="B209" t="s">
+        <v>4</v>
+      </c>
+      <c r="C209" t="s">
+        <v>5</v>
+      </c>
+      <c r="D209" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>539</v>
+      </c>
+      <c r="B210" t="s">
+        <v>4</v>
+      </c>
+      <c r="C210" t="s">
+        <v>5</v>
+      </c>
+      <c r="D210" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>540</v>
+      </c>
+      <c r="B211" t="s">
+        <v>4</v>
+      </c>
+      <c r="C211" t="s">
+        <v>5</v>
+      </c>
+      <c r="D211" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>541</v>
+      </c>
+      <c r="B212" t="s">
+        <v>7</v>
+      </c>
+      <c r="C212" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>542</v>
+      </c>
+      <c r="B213" t="s">
+        <v>4</v>
+      </c>
+      <c r="C213" t="s">
+        <v>5</v>
+      </c>
+      <c r="D213" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>543</v>
+      </c>
+      <c r="B214" t="s">
+        <v>4</v>
+      </c>
+      <c r="C214" t="s">
+        <v>5</v>
+      </c>
+      <c r="D214" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>544</v>
+      </c>
+      <c r="B215" t="s">
+        <v>4</v>
+      </c>
+      <c r="C215" t="s">
+        <v>5</v>
+      </c>
+      <c r="D215" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>545</v>
+      </c>
+      <c r="B216" t="s">
+        <v>4</v>
+      </c>
+      <c r="C216" t="s">
+        <v>5</v>
+      </c>
+      <c r="D216" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>546</v>
+      </c>
+      <c r="B217" t="s">
+        <v>4</v>
+      </c>
+      <c r="C217" t="s">
+        <v>5</v>
+      </c>
+      <c r="D217" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>547</v>
+      </c>
+      <c r="B218" t="s">
+        <v>4</v>
+      </c>
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>548</v>
+      </c>
+      <c r="B219" t="s">
+        <v>4</v>
+      </c>
+      <c r="C219" t="s">
+        <v>5</v>
+      </c>
+      <c r="D219" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>549</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4</v>
+      </c>
+      <c r="C220" t="s">
+        <v>5</v>
+      </c>
+      <c r="D220" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>550</v>
+      </c>
+      <c r="B221" t="s">
+        <v>4</v>
+      </c>
+      <c r="C221" t="s">
+        <v>5</v>
+      </c>
+      <c r="D221" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>551</v>
+      </c>
+      <c r="B222" t="s">
+        <v>4</v>
+      </c>
+      <c r="C222" t="s">
+        <v>5</v>
+      </c>
+      <c r="D222" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>552</v>
+      </c>
+      <c r="B223" t="s">
+        <v>4</v>
+      </c>
+      <c r="C223" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>553</v>
+      </c>
+      <c r="B224" t="s">
+        <v>4</v>
+      </c>
+      <c r="C224" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>554</v>
+      </c>
+      <c r="B225" t="s">
+        <v>4</v>
+      </c>
+      <c r="C225" t="s">
+        <v>5</v>
+      </c>
+      <c r="D225" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>555</v>
+      </c>
+      <c r="B226" t="s">
+        <v>7</v>
+      </c>
+      <c r="C226" t="s">
+        <v>8</v>
+      </c>
+      <c r="D226" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>556</v>
+      </c>
+      <c r="B227" t="s">
+        <v>4</v>
+      </c>
+      <c r="C227" t="s">
+        <v>5</v>
+      </c>
+      <c r="D227" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>557</v>
+      </c>
+      <c r="B228" t="s">
+        <v>4</v>
+      </c>
+      <c r="C228" t="s">
+        <v>5</v>
+      </c>
+      <c r="D228" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>558</v>
+      </c>
+      <c r="B229" t="s">
+        <v>4</v>
+      </c>
+      <c r="C229" t="s">
+        <v>5</v>
+      </c>
+      <c r="D229" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>559</v>
+      </c>
+      <c r="B230" t="s">
+        <v>4</v>
+      </c>
+      <c r="C230" t="s">
+        <v>5</v>
+      </c>
+      <c r="D230" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>1</v>
+      </c>
+      <c r="B231" t="s">
+        <v>7</v>
+      </c>
+      <c r="C231" t="s">
+        <v>8</v>
+      </c>
+      <c r="D231" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>2</v>
+      </c>
+      <c r="B232" t="s">
+        <v>7</v>
+      </c>
+      <c r="C232" t="s">
+        <v>8</v>
+      </c>
+      <c r="D232" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>3</v>
+      </c>
+      <c r="B233" t="s">
+        <v>7</v>
+      </c>
+      <c r="C233" t="s">
+        <v>8</v>
+      </c>
+      <c r="D233" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>4</v>
+      </c>
+      <c r="B234" t="s">
+        <v>7</v>
+      </c>
+      <c r="C234" t="s">
+        <v>8</v>
+      </c>
+      <c r="D234" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>5</v>
+      </c>
+      <c r="B235" t="s">
+        <v>7</v>
+      </c>
+      <c r="C235" t="s">
+        <v>8</v>
+      </c>
+      <c r="D235" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>6</v>
+      </c>
+      <c r="B236" t="s">
+        <v>7</v>
+      </c>
+      <c r="C236" t="s">
+        <v>8</v>
+      </c>
+      <c r="D236" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>7</v>
+      </c>
+      <c r="B237" t="s">
+        <v>7</v>
+      </c>
+      <c r="C237" t="s">
+        <v>8</v>
+      </c>
+      <c r="D237" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>8</v>
+      </c>
+      <c r="B238" t="s">
+        <v>7</v>
+      </c>
+      <c r="C238" t="s">
+        <v>8</v>
+      </c>
+      <c r="D238" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>9</v>
+      </c>
+      <c r="B239" t="s">
+        <v>7</v>
+      </c>
+      <c r="C239" t="s">
+        <v>8</v>
+      </c>
+      <c r="D239" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>10</v>
+      </c>
+      <c r="B240" t="s">
+        <v>7</v>
+      </c>
+      <c r="C240" t="s">
+        <v>8</v>
+      </c>
+      <c r="D240" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>11</v>
+      </c>
+      <c r="B241" t="s">
+        <v>7</v>
+      </c>
+      <c r="C241" t="s">
+        <v>8</v>
+      </c>
+      <c r="D241" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>12</v>
+      </c>
+      <c r="B242" t="s">
+        <v>7</v>
+      </c>
+      <c r="C242" t="s">
+        <v>8</v>
+      </c>
+      <c r="D242" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>13</v>
+      </c>
+      <c r="B243" t="s">
+        <v>7</v>
+      </c>
+      <c r="C243" t="s">
+        <v>8</v>
+      </c>
+      <c r="D243" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>14</v>
+      </c>
+      <c r="B244" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" t="s">
+        <v>8</v>
+      </c>
+      <c r="D244" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>15</v>
+      </c>
+      <c r="B245" t="s">
+        <v>7</v>
+      </c>
+      <c r="C245" t="s">
+        <v>8</v>
+      </c>
+      <c r="D245" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>16</v>
+      </c>
+      <c r="B246" t="s">
+        <v>7</v>
+      </c>
+      <c r="C246" t="s">
+        <v>8</v>
+      </c>
+      <c r="D246" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>17</v>
+      </c>
+      <c r="B247" t="s">
+        <v>7</v>
+      </c>
+      <c r="C247" t="s">
+        <v>8</v>
+      </c>
+      <c r="D247" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>19</v>
+      </c>
+      <c r="B248" t="s">
+        <v>7</v>
+      </c>
+      <c r="C248" t="s">
+        <v>8</v>
+      </c>
+      <c r="D248" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>34</v>
+      </c>
+      <c r="B249" t="s">
+        <v>7</v>
+      </c>
+      <c r="C249" t="s">
+        <v>8</v>
+      </c>
+      <c r="D249" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>39</v>
+      </c>
+      <c r="B250" t="s">
+        <v>7</v>
+      </c>
+      <c r="C250" t="s">
+        <v>8</v>
+      </c>
+      <c r="D250" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>41</v>
+      </c>
+      <c r="B251" t="s">
+        <v>7</v>
+      </c>
+      <c r="C251" t="s">
+        <v>8</v>
+      </c>
+      <c r="D251" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>62</v>
+      </c>
+      <c r="B252" t="s">
+        <v>7</v>
+      </c>
+      <c r="C252" t="s">
+        <v>8</v>
+      </c>
+      <c r="D252" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>64</v>
+      </c>
+      <c r="B253" t="s">
+        <v>7</v>
+      </c>
+      <c r="C253" t="s">
+        <v>8</v>
+      </c>
+      <c r="D253" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>70</v>
+      </c>
+      <c r="B254" t="s">
+        <v>7</v>
+      </c>
+      <c r="C254" t="s">
+        <v>8</v>
+      </c>
+      <c r="D254" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>84</v>
+      </c>
+      <c r="B255" t="s">
+        <v>7</v>
+      </c>
+      <c r="C255" t="s">
+        <v>8</v>
+      </c>
+      <c r="D255" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>89</v>
+      </c>
+      <c r="B256" t="s">
+        <v>7</v>
+      </c>
+      <c r="C256" t="s">
+        <v>8</v>
+      </c>
+      <c r="D256" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>91</v>
+      </c>
+      <c r="B257" t="s">
+        <v>7</v>
+      </c>
+      <c r="C257" t="s">
+        <v>8</v>
+      </c>
+      <c r="D257" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>108</v>
+      </c>
+      <c r="B258" t="s">
+        <v>7</v>
+      </c>
+      <c r="C258" t="s">
+        <v>8</v>
+      </c>
+      <c r="D258" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>110</v>
+      </c>
+      <c r="B259" t="s">
+        <v>7</v>
+      </c>
+      <c r="C259" t="s">
+        <v>8</v>
+      </c>
+      <c r="D259" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>457</v>
+      </c>
+      <c r="B260" t="s">
+        <v>7</v>
+      </c>
+      <c r="C260" t="s">
+        <v>8</v>
+      </c>
+      <c r="D260" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>458</v>
+      </c>
+      <c r="B261" t="s">
+        <v>7</v>
+      </c>
+      <c r="C261" t="s">
+        <v>8</v>
+      </c>
+      <c r="D261" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>459</v>
+      </c>
+      <c r="B262" t="s">
+        <v>7</v>
+      </c>
+      <c r="C262" t="s">
+        <v>8</v>
+      </c>
+      <c r="D262" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>460</v>
+      </c>
+      <c r="B263" t="s">
+        <v>7</v>
+      </c>
+      <c r="C263" t="s">
+        <v>8</v>
+      </c>
+      <c r="D263" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>461</v>
+      </c>
+      <c r="B264" t="s">
+        <v>7</v>
+      </c>
+      <c r="C264" t="s">
+        <v>8</v>
+      </c>
+      <c r="D264" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>462</v>
+      </c>
+      <c r="B265" t="s">
+        <v>7</v>
+      </c>
+      <c r="C265" t="s">
+        <v>8</v>
+      </c>
+      <c r="D265" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>463</v>
+      </c>
+      <c r="B266" t="s">
+        <v>7</v>
+      </c>
+      <c r="C266" t="s">
+        <v>8</v>
+      </c>
+      <c r="D266" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>464</v>
+      </c>
+      <c r="B267" t="s">
+        <v>7</v>
+      </c>
+      <c r="C267" t="s">
+        <v>8</v>
+      </c>
+      <c r="D267" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>465</v>
+      </c>
+      <c r="B268" t="s">
+        <v>7</v>
+      </c>
+      <c r="C268" t="s">
+        <v>8</v>
+      </c>
+      <c r="D268" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>466</v>
+      </c>
+      <c r="B269" t="s">
+        <v>7</v>
+      </c>
+      <c r="C269" t="s">
+        <v>8</v>
+      </c>
+      <c r="D269" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>467</v>
+      </c>
+      <c r="B270" t="s">
+        <v>7</v>
+      </c>
+      <c r="C270" t="s">
+        <v>8</v>
+      </c>
+      <c r="D270" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>468</v>
+      </c>
+      <c r="B271" t="s">
+        <v>7</v>
+      </c>
+      <c r="C271" t="s">
+        <v>8</v>
+      </c>
+      <c r="D271" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>469</v>
+      </c>
+      <c r="B272" t="s">
+        <v>7</v>
+      </c>
+      <c r="C272" t="s">
+        <v>8</v>
+      </c>
+      <c r="D272" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>470</v>
+      </c>
+      <c r="B273" t="s">
+        <v>7</v>
+      </c>
+      <c r="C273" t="s">
+        <v>8</v>
+      </c>
+      <c r="D273" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>471</v>
+      </c>
+      <c r="B274" t="s">
+        <v>7</v>
+      </c>
+      <c r="C274" t="s">
+        <v>8</v>
+      </c>
+      <c r="D274" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>472</v>
+      </c>
+      <c r="B275" t="s">
+        <v>7</v>
+      </c>
+      <c r="C275" t="s">
+        <v>8</v>
+      </c>
+      <c r="D275" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>473</v>
+      </c>
+      <c r="B276" t="s">
+        <v>7</v>
+      </c>
+      <c r="C276" t="s">
+        <v>8</v>
+      </c>
+      <c r="D276" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>474</v>
+      </c>
+      <c r="B277" t="s">
+        <v>7</v>
+      </c>
+      <c r="C277" t="s">
+        <v>8</v>
+      </c>
+      <c r="D277" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>475</v>
+      </c>
+      <c r="B278" t="s">
+        <v>7</v>
+      </c>
+      <c r="C278" t="s">
+        <v>8</v>
+      </c>
+      <c r="D278" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>476</v>
+      </c>
+      <c r="B279" t="s">
+        <v>7</v>
+      </c>
+      <c r="C279" t="s">
+        <v>8</v>
+      </c>
+      <c r="D279" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>477</v>
+      </c>
+      <c r="B280" t="s">
+        <v>7</v>
+      </c>
+      <c r="C280" t="s">
+        <v>8</v>
+      </c>
+      <c r="D280" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>478</v>
+      </c>
+      <c r="B281" t="s">
+        <v>7</v>
+      </c>
+      <c r="C281" t="s">
+        <v>8</v>
+      </c>
+      <c r="D281" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>479</v>
+      </c>
+      <c r="B282" t="s">
+        <v>7</v>
+      </c>
+      <c r="C282" t="s">
+        <v>8</v>
+      </c>
+      <c r="D282" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>480</v>
+      </c>
+      <c r="B283" t="s">
+        <v>7</v>
+      </c>
+      <c r="C283" t="s">
+        <v>8</v>
+      </c>
+      <c r="D283" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>481</v>
+      </c>
+      <c r="B284" t="s">
+        <v>7</v>
+      </c>
+      <c r="C284" t="s">
+        <v>8</v>
+      </c>
+      <c r="D284" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>482</v>
+      </c>
+      <c r="B285" t="s">
+        <v>7</v>
+      </c>
+      <c r="C285" t="s">
+        <v>8</v>
+      </c>
+      <c r="D285" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>483</v>
+      </c>
+      <c r="B286" t="s">
+        <v>7</v>
+      </c>
+      <c r="C286" t="s">
+        <v>8</v>
+      </c>
+      <c r="D286" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>484</v>
+      </c>
+      <c r="B287" t="s">
+        <v>7</v>
+      </c>
+      <c r="C287" t="s">
+        <v>8</v>
+      </c>
+      <c r="D287" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>485</v>
+      </c>
+      <c r="B288" t="s">
+        <v>7</v>
+      </c>
+      <c r="C288" t="s">
+        <v>8</v>
+      </c>
+      <c r="D288" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>486</v>
+      </c>
+      <c r="B289" t="s">
+        <v>7</v>
+      </c>
+      <c r="C289" t="s">
+        <v>8</v>
+      </c>
+      <c r="D289" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>487</v>
+      </c>
+      <c r="B290" t="s">
+        <v>7</v>
+      </c>
+      <c r="C290" t="s">
+        <v>8</v>
+      </c>
+      <c r="D290" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>488</v>
+      </c>
+      <c r="B291" t="s">
+        <v>7</v>
+      </c>
+      <c r="C291" t="s">
+        <v>8</v>
+      </c>
+      <c r="D291" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>490</v>
+      </c>
+      <c r="B292" t="s">
+        <v>7</v>
+      </c>
+      <c r="C292" t="s">
+        <v>8</v>
+      </c>
+      <c r="D292" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>505</v>
+      </c>
+      <c r="B293" t="s">
+        <v>7</v>
+      </c>
+      <c r="C293" t="s">
+        <v>8</v>
+      </c>
+      <c r="D293" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>510</v>
+      </c>
+      <c r="B294" t="s">
+        <v>7</v>
+      </c>
+      <c r="C294" t="s">
+        <v>8</v>
+      </c>
+      <c r="D294" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>512</v>
+      </c>
+      <c r="B295" t="s">
+        <v>7</v>
+      </c>
+      <c r="C295" t="s">
+        <v>8</v>
+      </c>
+      <c r="D295" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>533</v>
+      </c>
+      <c r="B296" t="s">
+        <v>7</v>
+      </c>
+      <c r="C296" t="s">
+        <v>8</v>
+      </c>
+      <c r="D296" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>535</v>
+      </c>
+      <c r="B297" t="s">
+        <v>7</v>
+      </c>
+      <c r="C297" t="s">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>541</v>
+      </c>
+      <c r="B298" t="s">
+        <v>7</v>
+      </c>
+      <c r="C298" t="s">
+        <v>8</v>
+      </c>
+      <c r="D298" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>555</v>
+      </c>
+      <c r="B299" t="s">
+        <v>7</v>
+      </c>
+      <c r="C299" t="s">
+        <v>8</v>
+      </c>
+      <c r="D299" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>560</v>
+      </c>
+      <c r="B300" t="s">
+        <v>7</v>
+      </c>
+      <c r="C300" t="s">
+        <v>8</v>
+      </c>
+      <c r="D300" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>561</v>
+      </c>
+      <c r="B301" t="s">
+        <v>4</v>
+      </c>
+      <c r="C301" t="s">
+        <v>5</v>
+      </c>
+      <c r="D301" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>562</v>
+      </c>
+      <c r="B302" t="s">
+        <v>7</v>
+      </c>
+      <c r="C302" t="s">
+        <v>8</v>
+      </c>
+      <c r="D302" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>563</v>
+      </c>
+      <c r="B303" t="s">
+        <v>4</v>
+      </c>
+      <c r="C303" t="s">
+        <v>5</v>
+      </c>
+      <c r="D303" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>564</v>
+      </c>
+      <c r="B304" t="s">
+        <v>4</v>
+      </c>
+      <c r="C304" t="s">
+        <v>5</v>
+      </c>
+      <c r="D304" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>565</v>
+      </c>
+      <c r="B305" t="s">
+        <v>4</v>
+      </c>
+      <c r="C305" t="s">
+        <v>5</v>
+      </c>
+      <c r="D305" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>566</v>
+      </c>
+      <c r="B306" t="s">
+        <v>4</v>
+      </c>
+      <c r="C306" t="s">
+        <v>5</v>
+      </c>
+      <c r="D306" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>567</v>
+      </c>
+      <c r="B307" t="s">
+        <v>4</v>
+      </c>
+      <c r="C307" t="s">
+        <v>5</v>
+      </c>
+      <c r="D307" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>568</v>
+      </c>
+      <c r="B308" t="s">
+        <v>4</v>
+      </c>
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+      <c r="D308" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>569</v>
+      </c>
+      <c r="B309" t="s">
+        <v>4</v>
+      </c>
+      <c r="C309" t="s">
+        <v>5</v>
+      </c>
+      <c r="D309" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>570</v>
+      </c>
+      <c r="B310" t="s">
+        <v>4</v>
+      </c>
+      <c r="C310" t="s">
+        <v>5</v>
+      </c>
+      <c r="D310" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>571</v>
+      </c>
+      <c r="B311" t="s">
+        <v>4</v>
+      </c>
+      <c r="C311" t="s">
+        <v>5</v>
+      </c>
+      <c r="D311" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>572</v>
+      </c>
+      <c r="B312" t="s">
+        <v>4</v>
+      </c>
+      <c r="C312" t="s">
+        <v>5</v>
+      </c>
+      <c r="D312" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>573</v>
+      </c>
+      <c r="B313" t="s">
+        <v>4</v>
+      </c>
+      <c r="C313" t="s">
+        <v>5</v>
+      </c>
+      <c r="D313" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>574</v>
+      </c>
+      <c r="B314" t="s">
+        <v>4</v>
+      </c>
+      <c r="C314" t="s">
+        <v>5</v>
+      </c>
+      <c r="D314" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>575</v>
+      </c>
+      <c r="B315" t="s">
+        <v>4</v>
+      </c>
+      <c r="C315" t="s">
+        <v>5</v>
+      </c>
+      <c r="D315" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>576</v>
+      </c>
+      <c r="B316" t="s">
+        <v>4</v>
+      </c>
+      <c r="C316" t="s">
+        <v>5</v>
+      </c>
+      <c r="D316" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>577</v>
+      </c>
+      <c r="B317" t="s">
+        <v>4</v>
+      </c>
+      <c r="C317" t="s">
+        <v>5</v>
+      </c>
+      <c r="D317" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>578</v>
+      </c>
+      <c r="B318" t="s">
+        <v>4</v>
+      </c>
+      <c r="C318" t="s">
+        <v>5</v>
+      </c>
+      <c r="D318" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>579</v>
+      </c>
+      <c r="B319" t="s">
+        <v>7</v>
+      </c>
+      <c r="C319" t="s">
+        <v>8</v>
+      </c>
+      <c r="D319" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>580</v>
+      </c>
+      <c r="B320" t="s">
+        <v>4</v>
+      </c>
+      <c r="C320" t="s">
+        <v>5</v>
+      </c>
+      <c r="D320" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>581</v>
+      </c>
+      <c r="B321" t="s">
+        <v>7</v>
+      </c>
+      <c r="C321" t="s">
+        <v>8</v>
+      </c>
+      <c r="D321" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>582</v>
+      </c>
+      <c r="B322" t="s">
+        <v>4</v>
+      </c>
+      <c r="C322" t="s">
+        <v>5</v>
+      </c>
+      <c r="D322" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>583</v>
+      </c>
+      <c r="B323" t="s">
+        <v>4</v>
+      </c>
+      <c r="C323" t="s">
+        <v>5</v>
+      </c>
+      <c r="D323" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>584</v>
+      </c>
+      <c r="B324" t="s">
+        <v>4</v>
+      </c>
+      <c r="C324" t="s">
+        <v>5</v>
+      </c>
+      <c r="D324" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>585</v>
+      </c>
+      <c r="B325" t="s">
+        <v>4</v>
+      </c>
+      <c r="C325" t="s">
+        <v>5</v>
+      </c>
+      <c r="D325" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>586</v>
+      </c>
+      <c r="B326" t="s">
+        <v>7</v>
+      </c>
+      <c r="C326" t="s">
+        <v>8</v>
+      </c>
+      <c r="D326" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>587</v>
+      </c>
+      <c r="B327" t="s">
+        <v>7</v>
+      </c>
+      <c r="C327" t="s">
+        <v>8</v>
+      </c>
+      <c r="D327" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>588</v>
+      </c>
+      <c r="B328" t="s">
+        <v>7</v>
+      </c>
+      <c r="C328" t="s">
+        <v>8</v>
+      </c>
+      <c r="D328" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>589</v>
+      </c>
+      <c r="B329" t="s">
+        <v>7</v>
+      </c>
+      <c r="C329" t="s">
+        <v>8</v>
+      </c>
+      <c r="D329" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>590</v>
+      </c>
+      <c r="B330" t="s">
+        <v>7</v>
+      </c>
+      <c r="C330" t="s">
+        <v>8</v>
+      </c>
+      <c r="D330" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>591</v>
+      </c>
+      <c r="B331" t="s">
+        <v>7</v>
+      </c>
+      <c r="C331" t="s">
+        <v>8</v>
+      </c>
+      <c r="D331" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>592</v>
+      </c>
+      <c r="B332" t="s">
+        <v>7</v>
+      </c>
+      <c r="C332" t="s">
+        <v>8</v>
+      </c>
+      <c r="D332" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>593</v>
+      </c>
+      <c r="B333" t="s">
+        <v>7</v>
+      </c>
+      <c r="C333" t="s">
+        <v>8</v>
+      </c>
+      <c r="D333" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>594</v>
+      </c>
+      <c r="B334" t="s">
+        <v>7</v>
+      </c>
+      <c r="C334" t="s">
+        <v>8</v>
+      </c>
+      <c r="D334" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>595</v>
+      </c>
+      <c r="B335" t="s">
+        <v>7</v>
+      </c>
+      <c r="C335" t="s">
+        <v>8</v>
+      </c>
+      <c r="D335" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>596</v>
+      </c>
+      <c r="B336" t="s">
+        <v>7</v>
+      </c>
+      <c r="C336" t="s">
+        <v>8</v>
+      </c>
+      <c r="D336" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>597</v>
+      </c>
+      <c r="B337" t="s">
+        <v>7</v>
+      </c>
+      <c r="C337" t="s">
+        <v>8</v>
+      </c>
+      <c r="D337" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>598</v>
+      </c>
+      <c r="B338" t="s">
+        <v>7</v>
+      </c>
+      <c r="C338" t="s">
+        <v>8</v>
+      </c>
+      <c r="D338" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>599</v>
+      </c>
+      <c r="B339" t="s">
+        <v>7</v>
+      </c>
+      <c r="C339" t="s">
+        <v>8</v>
+      </c>
+      <c r="D339" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>600</v>
+      </c>
+      <c r="B340" t="s">
+        <v>7</v>
+      </c>
+      <c r="C340" t="s">
+        <v>8</v>
+      </c>
+      <c r="D340" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>601</v>
+      </c>
+      <c r="B341" t="s">
+        <v>7</v>
+      </c>
+      <c r="C341" t="s">
+        <v>8</v>
+      </c>
+      <c r="D341" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>602</v>
+      </c>
+      <c r="B342" t="s">
+        <v>7</v>
+      </c>
+      <c r="C342" t="s">
+        <v>8</v>
+      </c>
+      <c r="D342" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>603</v>
+      </c>
+      <c r="B343" t="s">
+        <v>7</v>
+      </c>
+      <c r="C343" t="s">
+        <v>8</v>
+      </c>
+      <c r="D343" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>604</v>
+      </c>
+      <c r="B344" t="s">
+        <v>7</v>
+      </c>
+      <c r="C344" t="s">
+        <v>8</v>
+      </c>
+      <c r="D344" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>605</v>
+      </c>
+      <c r="B345" t="s">
+        <v>7</v>
+      </c>
+      <c r="C345" t="s">
+        <v>8</v>
+      </c>
+      <c r="D345" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>606</v>
+      </c>
+      <c r="B346" t="s">
+        <v>7</v>
+      </c>
+      <c r="C346" t="s">
+        <v>8</v>
+      </c>
+      <c r="D346" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>607</v>
+      </c>
+      <c r="B347" t="s">
+        <v>7</v>
+      </c>
+      <c r="C347" t="s">
+        <v>8</v>
+      </c>
+      <c r="D347" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>608</v>
+      </c>
+      <c r="B348" t="s">
+        <v>7</v>
+      </c>
+      <c r="C348" t="s">
+        <v>8</v>
+      </c>
+      <c r="D348" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>609</v>
+      </c>
+      <c r="B349" t="s">
+        <v>7</v>
+      </c>
+      <c r="C349" t="s">
+        <v>8</v>
+      </c>
+      <c r="D349" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>610</v>
+      </c>
+      <c r="B350" t="s">
+        <v>7</v>
+      </c>
+      <c r="C350" t="s">
+        <v>8</v>
+      </c>
+      <c r="D350" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>611</v>
+      </c>
+      <c r="B351" t="s">
+        <v>7</v>
+      </c>
+      <c r="C351" t="s">
+        <v>8</v>
+      </c>
+      <c r="D351" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>612</v>
+      </c>
+      <c r="B352" t="s">
+        <v>7</v>
+      </c>
+      <c r="C352" t="s">
+        <v>8</v>
+      </c>
+      <c r="D352" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>613</v>
+      </c>
+      <c r="B353" t="s">
+        <v>7</v>
+      </c>
+      <c r="C353" t="s">
+        <v>8</v>
+      </c>
+      <c r="D353" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>614</v>
+      </c>
+      <c r="B354" t="s">
+        <v>7</v>
+      </c>
+      <c r="C354" t="s">
+        <v>8</v>
+      </c>
+      <c r="D354" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>615</v>
+      </c>
+      <c r="B355" t="s">
+        <v>7</v>
+      </c>
+      <c r="C355" t="s">
+        <v>8</v>
+      </c>
+      <c r="D355" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>616</v>
+      </c>
+      <c r="B356" t="s">
+        <v>7</v>
+      </c>
+      <c r="C356" t="s">
+        <v>8</v>
+      </c>
+      <c r="D356" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>617</v>
+      </c>
+      <c r="B357" t="s">
+        <v>7</v>
+      </c>
+      <c r="C357" t="s">
+        <v>8</v>
+      </c>
+      <c r="D357" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>618</v>
+      </c>
+      <c r="B358" t="s">
+        <v>4</v>
+      </c>
+      <c r="C358" t="s">
+        <v>5</v>
+      </c>
+      <c r="D358" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>619</v>
+      </c>
+      <c r="B359" t="s">
+        <v>7</v>
+      </c>
+      <c r="C359" t="s">
+        <v>8</v>
+      </c>
+      <c r="D359" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>620</v>
+      </c>
+      <c r="B360" t="s">
+        <v>4</v>
+      </c>
+      <c r="C360" t="s">
+        <v>5</v>
+      </c>
+      <c r="D360" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>621</v>
+      </c>
+      <c r="B361" t="s">
+        <v>4</v>
+      </c>
+      <c r="C361" t="s">
+        <v>5</v>
+      </c>
+      <c r="D361" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>622</v>
+      </c>
+      <c r="B362" t="s">
+        <v>4</v>
+      </c>
+      <c r="C362" t="s">
+        <v>5</v>
+      </c>
+      <c r="D362" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>623</v>
+      </c>
+      <c r="B363" t="s">
+        <v>4</v>
+      </c>
+      <c r="C363" t="s">
+        <v>5</v>
+      </c>
+      <c r="D363" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>624</v>
+      </c>
+      <c r="B364" t="s">
+        <v>4</v>
+      </c>
+      <c r="C364" t="s">
+        <v>5</v>
+      </c>
+      <c r="D364" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>625</v>
+      </c>
+      <c r="B365" t="s">
+        <v>4</v>
+      </c>
+      <c r="C365" t="s">
+        <v>5</v>
+      </c>
+      <c r="D365" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>626</v>
+      </c>
+      <c r="B366" t="s">
+        <v>4</v>
+      </c>
+      <c r="C366" t="s">
+        <v>5</v>
+      </c>
+      <c r="D366" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>627</v>
+      </c>
+      <c r="B367" t="s">
+        <v>4</v>
+      </c>
+      <c r="C367" t="s">
+        <v>5</v>
+      </c>
+      <c r="D367" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>628</v>
+      </c>
+      <c r="B368" t="s">
+        <v>4</v>
+      </c>
+      <c r="C368" t="s">
+        <v>5</v>
+      </c>
+      <c r="D368" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>629</v>
+      </c>
+      <c r="B369" t="s">
+        <v>4</v>
+      </c>
+      <c r="C369" t="s">
+        <v>5</v>
+      </c>
+      <c r="D369" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>630</v>
+      </c>
+      <c r="B370" t="s">
+        <v>4</v>
+      </c>
+      <c r="C370" t="s">
+        <v>5</v>
+      </c>
+      <c r="D370" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>631</v>
+      </c>
+      <c r="B371" t="s">
+        <v>4</v>
+      </c>
+      <c r="C371" t="s">
+        <v>5</v>
+      </c>
+      <c r="D371" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>632</v>
+      </c>
+      <c r="B372" t="s">
+        <v>4</v>
+      </c>
+      <c r="C372" t="s">
+        <v>5</v>
+      </c>
+      <c r="D372" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>633</v>
+      </c>
+      <c r="B373" t="s">
+        <v>4</v>
+      </c>
+      <c r="C373" t="s">
+        <v>5</v>
+      </c>
+      <c r="D373" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>634</v>
+      </c>
+      <c r="B374" t="s">
+        <v>7</v>
+      </c>
+      <c r="C374" t="s">
+        <v>8</v>
+      </c>
+      <c r="D374" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>635</v>
+      </c>
+      <c r="B375" t="s">
+        <v>4</v>
+      </c>
+      <c r="C375" t="s">
+        <v>5</v>
+      </c>
+      <c r="D375" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>636</v>
+      </c>
+      <c r="B376" t="s">
+        <v>4</v>
+      </c>
+      <c r="C376" t="s">
+        <v>5</v>
+      </c>
+      <c r="D376" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>637</v>
+      </c>
+      <c r="B377" t="s">
+        <v>4</v>
+      </c>
+      <c r="C377" t="s">
+        <v>5</v>
+      </c>
+      <c r="D377" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>638</v>
+      </c>
+      <c r="B378" t="s">
+        <v>4</v>
+      </c>
+      <c r="C378" t="s">
+        <v>5</v>
+      </c>
+      <c r="D378" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>639</v>
+      </c>
+      <c r="B379" t="s">
+        <v>7</v>
+      </c>
+      <c r="C379" t="s">
+        <v>8</v>
+      </c>
+      <c r="D379" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>640</v>
+      </c>
+      <c r="B380" t="s">
+        <v>4</v>
+      </c>
+      <c r="C380" t="s">
+        <v>5</v>
+      </c>
+      <c r="D380" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>641</v>
+      </c>
+      <c r="B381" t="s">
+        <v>7</v>
+      </c>
+      <c r="C381" t="s">
+        <v>8</v>
+      </c>
+      <c r="D381" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>642</v>
+      </c>
+      <c r="B382" t="s">
+        <v>4</v>
+      </c>
+      <c r="C382" t="s">
+        <v>5</v>
+      </c>
+      <c r="D382" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>643</v>
+      </c>
+      <c r="B383" t="s">
+        <v>4</v>
+      </c>
+      <c r="C383" t="s">
+        <v>5</v>
+      </c>
+      <c r="D383" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>644</v>
+      </c>
+      <c r="B384" t="s">
+        <v>4</v>
+      </c>
+      <c r="C384" t="s">
+        <v>5</v>
+      </c>
+      <c r="D384" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>645</v>
+      </c>
+      <c r="B385" t="s">
+        <v>4</v>
+      </c>
+      <c r="C385" t="s">
+        <v>5</v>
+      </c>
+      <c r="D385" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>646</v>
+      </c>
+      <c r="B386" t="s">
+        <v>4</v>
+      </c>
+      <c r="C386" t="s">
+        <v>5</v>
+      </c>
+      <c r="D386" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>647</v>
+      </c>
+      <c r="B387" t="s">
+        <v>4</v>
+      </c>
+      <c r="C387" t="s">
+        <v>5</v>
+      </c>
+      <c r="D387" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>648</v>
+      </c>
+      <c r="B388" t="s">
+        <v>4</v>
+      </c>
+      <c r="C388" t="s">
+        <v>5</v>
+      </c>
+      <c r="D388" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>649</v>
+      </c>
+      <c r="B389" t="s">
+        <v>4</v>
+      </c>
+      <c r="C389" t="s">
+        <v>5</v>
+      </c>
+      <c r="D389" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>650</v>
+      </c>
+      <c r="B390" t="s">
+        <v>4</v>
+      </c>
+      <c r="C390" t="s">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>651</v>
+      </c>
+      <c r="B391" t="s">
+        <v>4</v>
+      </c>
+      <c r="C391" t="s">
+        <v>5</v>
+      </c>
+      <c r="D391" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>652</v>
+      </c>
+      <c r="B392" t="s">
+        <v>4</v>
+      </c>
+      <c r="C392" t="s">
+        <v>5</v>
+      </c>
+      <c r="D392" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>653</v>
+      </c>
+      <c r="B393" t="s">
+        <v>4</v>
+      </c>
+      <c r="C393" t="s">
+        <v>5</v>
+      </c>
+      <c r="D393" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>654</v>
+      </c>
+      <c r="B394" t="s">
+        <v>4</v>
+      </c>
+      <c r="C394" t="s">
+        <v>5</v>
+      </c>
+      <c r="D394" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>655</v>
+      </c>
+      <c r="B395" t="s">
+        <v>4</v>
+      </c>
+      <c r="C395" t="s">
+        <v>5</v>
+      </c>
+      <c r="D395" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>656</v>
+      </c>
+      <c r="B396" t="s">
+        <v>4</v>
+      </c>
+      <c r="C396" t="s">
+        <v>5</v>
+      </c>
+      <c r="D396" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>657</v>
+      </c>
+      <c r="B397" t="s">
+        <v>4</v>
+      </c>
+      <c r="C397" t="s">
+        <v>5</v>
+      </c>
+      <c r="D397" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>658</v>
+      </c>
+      <c r="B398" t="s">
+        <v>4</v>
+      </c>
+      <c r="C398" t="s">
+        <v>5</v>
+      </c>
+      <c r="D398" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>659</v>
+      </c>
+      <c r="B399" t="s">
+        <v>4</v>
+      </c>
+      <c r="C399" t="s">
+        <v>5</v>
+      </c>
+      <c r="D399" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>660</v>
+      </c>
+      <c r="B400" t="s">
+        <v>4</v>
+      </c>
+      <c r="C400" t="s">
+        <v>5</v>
+      </c>
+      <c r="D400" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>661</v>
+      </c>
+      <c r="B401" t="s">
+        <v>4</v>
+      </c>
+      <c r="C401" t="s">
+        <v>5</v>
+      </c>
+      <c r="D401" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>662</v>
+      </c>
+      <c r="B402" t="s">
+        <v>7</v>
+      </c>
+      <c r="C402" t="s">
+        <v>8</v>
+      </c>
+      <c r="D402" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>663</v>
+      </c>
+      <c r="B403" t="s">
+        <v>4</v>
+      </c>
+      <c r="C403" t="s">
+        <v>5</v>
+      </c>
+      <c r="D403" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>664</v>
+      </c>
+      <c r="B404" t="s">
+        <v>7</v>
+      </c>
+      <c r="C404" t="s">
+        <v>8</v>
+      </c>
+      <c r="D404" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>665</v>
+      </c>
+      <c r="B405" t="s">
+        <v>4</v>
+      </c>
+      <c r="C405" t="s">
+        <v>5</v>
+      </c>
+      <c r="D405" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>666</v>
+      </c>
+      <c r="B406" t="s">
+        <v>4</v>
+      </c>
+      <c r="C406" t="s">
+        <v>5</v>
+      </c>
+      <c r="D406" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>667</v>
+      </c>
+      <c r="B407" t="s">
+        <v>4</v>
+      </c>
+      <c r="C407" t="s">
+        <v>5</v>
+      </c>
+      <c r="D407" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>668</v>
+      </c>
+      <c r="B408" t="s">
+        <v>4</v>
+      </c>
+      <c r="C408" t="s">
+        <v>5</v>
+      </c>
+      <c r="D408" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>669</v>
+      </c>
+      <c r="B409" t="s">
+        <v>4</v>
+      </c>
+      <c r="C409" t="s">
+        <v>5</v>
+      </c>
+      <c r="D409" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>670</v>
+      </c>
+      <c r="B410" t="s">
+        <v>7</v>
+      </c>
+      <c r="C410" t="s">
+        <v>8</v>
+      </c>
+      <c r="D410" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>671</v>
+      </c>
+      <c r="B411" t="s">
+        <v>4</v>
+      </c>
+      <c r="C411" t="s">
+        <v>5</v>
+      </c>
+      <c r="D411" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>672</v>
+      </c>
+      <c r="B412" t="s">
+        <v>4</v>
+      </c>
+      <c r="C412" t="s">
+        <v>5</v>
+      </c>
+      <c r="D412" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>673</v>
+      </c>
+      <c r="B413" t="s">
+        <v>4</v>
+      </c>
+      <c r="C413" t="s">
+        <v>5</v>
+      </c>
+      <c r="D413" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>674</v>
+      </c>
+      <c r="B414" t="s">
+        <v>4</v>
+      </c>
+      <c r="C414" t="s">
+        <v>5</v>
+      </c>
+      <c r="D414" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>675</v>
+      </c>
+      <c r="B415" t="s">
+        <v>4</v>
+      </c>
+      <c r="C415" t="s">
+        <v>5</v>
+      </c>
+      <c r="D415" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A416">
+        <v>676</v>
+      </c>
+      <c r="B416" t="s">
+        <v>4</v>
+      </c>
+      <c r="C416" t="s">
+        <v>5</v>
+      </c>
+      <c r="D416" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>677</v>
+      </c>
+      <c r="B417" t="s">
+        <v>4</v>
+      </c>
+      <c r="C417" t="s">
+        <v>5</v>
+      </c>
+      <c r="D417" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>678</v>
+      </c>
+      <c r="B418" t="s">
+        <v>4</v>
+      </c>
+      <c r="C418" t="s">
+        <v>5</v>
+      </c>
+      <c r="D418" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>679</v>
+      </c>
+      <c r="B419" t="s">
+        <v>4</v>
+      </c>
+      <c r="C419" t="s">
+        <v>5</v>
+      </c>
+      <c r="D419" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>680</v>
+      </c>
+      <c r="B420" t="s">
+        <v>4</v>
+      </c>
+      <c r="C420" t="s">
+        <v>5</v>
+      </c>
+      <c r="D420" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>681</v>
+      </c>
+      <c r="B421" t="s">
+        <v>4</v>
+      </c>
+      <c r="C421" t="s">
+        <v>5</v>
+      </c>
+      <c r="D421" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>682</v>
+      </c>
+      <c r="B422" t="s">
+        <v>4</v>
+      </c>
+      <c r="C422" t="s">
+        <v>5</v>
+      </c>
+      <c r="D422" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>683</v>
+      </c>
+      <c r="B423" t="s">
+        <v>4</v>
+      </c>
+      <c r="C423" t="s">
+        <v>5</v>
+      </c>
+      <c r="D423" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>684</v>
+      </c>
+      <c r="B424" t="s">
+        <v>7</v>
+      </c>
+      <c r="C424" t="s">
+        <v>8</v>
+      </c>
+      <c r="D424" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>685</v>
+      </c>
+      <c r="B425" t="s">
+        <v>4</v>
+      </c>
+      <c r="C425" t="s">
+        <v>5</v>
+      </c>
+      <c r="D425" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>686</v>
+      </c>
+      <c r="B426" t="s">
+        <v>4</v>
+      </c>
+      <c r="C426" t="s">
+        <v>5</v>
+      </c>
+      <c r="D426" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>687</v>
+      </c>
+      <c r="B427" t="s">
+        <v>4</v>
+      </c>
+      <c r="C427" t="s">
+        <v>5</v>
+      </c>
+      <c r="D427" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>688</v>
+      </c>
+      <c r="B428" t="s">
+        <v>4</v>
+      </c>
+      <c r="C428" t="s">
+        <v>5</v>
+      </c>
+      <c r="D428" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>689</v>
+      </c>
+      <c r="B429" t="s">
+        <v>7</v>
+      </c>
+      <c r="C429" t="s">
+        <v>8</v>
+      </c>
+      <c r="D429" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>690</v>
+      </c>
+      <c r="B430" t="s">
+        <v>4</v>
+      </c>
+      <c r="C430" t="s">
+        <v>5</v>
+      </c>
+      <c r="D430" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>691</v>
+      </c>
+      <c r="B431" t="s">
+        <v>7</v>
+      </c>
+      <c r="C431" t="s">
+        <v>8</v>
+      </c>
+      <c r="D431" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>692</v>
+      </c>
+      <c r="B432" t="s">
+        <v>4</v>
+      </c>
+      <c r="C432" t="s">
+        <v>5</v>
+      </c>
+      <c r="D432" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>693</v>
+      </c>
+      <c r="B433" t="s">
+        <v>4</v>
+      </c>
+      <c r="C433" t="s">
+        <v>5</v>
+      </c>
+      <c r="D433" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>694</v>
+      </c>
+      <c r="B434" t="s">
+        <v>4</v>
+      </c>
+      <c r="C434" t="s">
+        <v>5</v>
+      </c>
+      <c r="D434" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>695</v>
+      </c>
+      <c r="B435" t="s">
+        <v>4</v>
+      </c>
+      <c r="C435" t="s">
+        <v>5</v>
+      </c>
+      <c r="D435" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>696</v>
+      </c>
+      <c r="B436" t="s">
+        <v>4</v>
+      </c>
+      <c r="C436" t="s">
+        <v>5</v>
+      </c>
+      <c r="D436" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>697</v>
+      </c>
+      <c r="B437" t="s">
+        <v>4</v>
+      </c>
+      <c r="C437" t="s">
+        <v>5</v>
+      </c>
+      <c r="D437" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>698</v>
+      </c>
+      <c r="B438" t="s">
+        <v>4</v>
+      </c>
+      <c r="C438" t="s">
+        <v>5</v>
+      </c>
+      <c r="D438" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>699</v>
+      </c>
+      <c r="B439" t="s">
+        <v>4</v>
+      </c>
+      <c r="C439" t="s">
+        <v>5</v>
+      </c>
+      <c r="D439" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>700</v>
+      </c>
+      <c r="B440" t="s">
+        <v>4</v>
+      </c>
+      <c r="C440" t="s">
+        <v>5</v>
+      </c>
+      <c r="D440" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>701</v>
+      </c>
+      <c r="B441" t="s">
+        <v>4</v>
+      </c>
+      <c r="C441" t="s">
+        <v>5</v>
+      </c>
+      <c r="D441" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>702</v>
+      </c>
+      <c r="B442" t="s">
+        <v>4</v>
+      </c>
+      <c r="C442" t="s">
+        <v>5</v>
+      </c>
+      <c r="D442" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>703</v>
+      </c>
+      <c r="B443" t="s">
+        <v>4</v>
+      </c>
+      <c r="C443" t="s">
+        <v>5</v>
+      </c>
+      <c r="D443" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>704</v>
+      </c>
+      <c r="B444" t="s">
+        <v>4</v>
+      </c>
+      <c r="C444" t="s">
+        <v>5</v>
+      </c>
+      <c r="D444" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>705</v>
+      </c>
+      <c r="B445" t="s">
+        <v>4</v>
+      </c>
+      <c r="C445" t="s">
+        <v>5</v>
+      </c>
+      <c r="D445" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>706</v>
+      </c>
+      <c r="B446" t="s">
+        <v>4</v>
+      </c>
+      <c r="C446" t="s">
+        <v>5</v>
+      </c>
+      <c r="D446" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>707</v>
+      </c>
+      <c r="B447" t="s">
+        <v>4</v>
+      </c>
+      <c r="C447" t="s">
+        <v>5</v>
+      </c>
+      <c r="D447" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>708</v>
+      </c>
+      <c r="B448" t="s">
+        <v>7</v>
+      </c>
+      <c r="C448" t="s">
+        <v>8</v>
+      </c>
+      <c r="D448" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>709</v>
+      </c>
+      <c r="B449" t="s">
+        <v>4</v>
+      </c>
+      <c r="C449" t="s">
+        <v>5</v>
+      </c>
+      <c r="D449" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>710</v>
+      </c>
+      <c r="B450" t="s">
+        <v>7</v>
+      </c>
+      <c r="C450" t="s">
+        <v>8</v>
+      </c>
+      <c r="D450" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>711</v>
+      </c>
+      <c r="B451" t="s">
+        <v>4</v>
+      </c>
+      <c r="C451" t="s">
+        <v>5</v>
+      </c>
+      <c r="D451" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>712</v>
+      </c>
+      <c r="B452" t="s">
+        <v>4</v>
+      </c>
+      <c r="C452" t="s">
+        <v>5</v>
+      </c>
+      <c r="D452" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>713</v>
+      </c>
+      <c r="B453" t="s">
+        <v>4</v>
+      </c>
+      <c r="C453" t="s">
+        <v>5</v>
+      </c>
+      <c r="D453" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>714</v>
+      </c>
+      <c r="B454" t="s">
+        <v>4</v>
+      </c>
+      <c r="C454" t="s">
+        <v>5</v>
+      </c>
+      <c r="D454" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>715</v>
+      </c>
+      <c r="B455" t="s">
+        <v>7</v>
+      </c>
+      <c r="C455" t="s">
+        <v>8</v>
+      </c>
+      <c r="D455" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>716</v>
+      </c>
+      <c r="B456" t="s">
+        <v>7</v>
+      </c>
+      <c r="C456" t="s">
+        <v>8</v>
+      </c>
+      <c r="D456" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>717</v>
+      </c>
+      <c r="B457" t="s">
+        <v>7</v>
+      </c>
+      <c r="C457" t="s">
+        <v>8</v>
+      </c>
+      <c r="D457" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>718</v>
+      </c>
+      <c r="B458" t="s">
+        <v>7</v>
+      </c>
+      <c r="C458" t="s">
+        <v>8</v>
+      </c>
+      <c r="D458" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>719</v>
+      </c>
+      <c r="B459" t="s">
+        <v>7</v>
+      </c>
+      <c r="C459" t="s">
+        <v>8</v>
+      </c>
+      <c r="D459" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>720</v>
+      </c>
+      <c r="B460" t="s">
+        <v>7</v>
+      </c>
+      <c r="C460" t="s">
+        <v>8</v>
+      </c>
+      <c r="D460" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>721</v>
+      </c>
+      <c r="B461" t="s">
+        <v>7</v>
+      </c>
+      <c r="C461" t="s">
+        <v>8</v>
+      </c>
+      <c r="D461" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>722</v>
+      </c>
+      <c r="B462" t="s">
+        <v>7</v>
+      </c>
+      <c r="C462" t="s">
+        <v>8</v>
+      </c>
+      <c r="D462" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>723</v>
+      </c>
+      <c r="B463" t="s">
+        <v>7</v>
+      </c>
+      <c r="C463" t="s">
+        <v>8</v>
+      </c>
+      <c r="D463" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A464">
+        <v>724</v>
+      </c>
+      <c r="B464" t="s">
+        <v>7</v>
+      </c>
+      <c r="C464" t="s">
+        <v>8</v>
+      </c>
+      <c r="D464" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <v>725</v>
+      </c>
+      <c r="B465" t="s">
+        <v>7</v>
+      </c>
+      <c r="C465" t="s">
+        <v>8</v>
+      </c>
+      <c r="D465" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>726</v>
+      </c>
+      <c r="B466" t="s">
+        <v>7</v>
+      </c>
+      <c r="C466" t="s">
+        <v>8</v>
+      </c>
+      <c r="D466" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <v>727</v>
+      </c>
+      <c r="B467" t="s">
+        <v>7</v>
+      </c>
+      <c r="C467" t="s">
+        <v>8</v>
+      </c>
+      <c r="D467" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>728</v>
+      </c>
+      <c r="B468" t="s">
+        <v>7</v>
+      </c>
+      <c r="C468" t="s">
+        <v>8</v>
+      </c>
+      <c r="D468" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <v>729</v>
+      </c>
+      <c r="B469" t="s">
+        <v>7</v>
+      </c>
+      <c r="C469" t="s">
+        <v>8</v>
+      </c>
+      <c r="D469" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A470">
+        <v>730</v>
+      </c>
+      <c r="B470" t="s">
+        <v>7</v>
+      </c>
+      <c r="C470" t="s">
+        <v>8</v>
+      </c>
+      <c r="D470" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A471">
+        <v>731</v>
+      </c>
+      <c r="B471" t="s">
+        <v>7</v>
+      </c>
+      <c r="C471" t="s">
+        <v>8</v>
+      </c>
+      <c r="D471" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>732</v>
+      </c>
+      <c r="B472" t="s">
+        <v>7</v>
+      </c>
+      <c r="C472" t="s">
+        <v>8</v>
+      </c>
+      <c r="D472" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A473">
+        <v>733</v>
+      </c>
+      <c r="B473" t="s">
+        <v>7</v>
+      </c>
+      <c r="C473" t="s">
+        <v>8</v>
+      </c>
+      <c r="D473" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A474">
+        <v>734</v>
+      </c>
+      <c r="B474" t="s">
+        <v>7</v>
+      </c>
+      <c r="C474" t="s">
+        <v>8</v>
+      </c>
+      <c r="D474" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>735</v>
+      </c>
+      <c r="B475" t="s">
+        <v>7</v>
+      </c>
+      <c r="C475" t="s">
+        <v>8</v>
+      </c>
+      <c r="D475" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>736</v>
+      </c>
+      <c r="B476" t="s">
+        <v>7</v>
+      </c>
+      <c r="C476" t="s">
+        <v>8</v>
+      </c>
+      <c r="D476" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A477">
+        <v>737</v>
+      </c>
+      <c r="B477" t="s">
+        <v>7</v>
+      </c>
+      <c r="C477" t="s">
+        <v>8</v>
+      </c>
+      <c r="D477" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A478">
+        <v>738</v>
+      </c>
+      <c r="B478" t="s">
+        <v>7</v>
+      </c>
+      <c r="C478" t="s">
+        <v>8</v>
+      </c>
+      <c r="D478" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A479">
+        <v>739</v>
+      </c>
+      <c r="B479" t="s">
+        <v>7</v>
+      </c>
+      <c r="C479" t="s">
+        <v>8</v>
+      </c>
+      <c r="D479" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>740</v>
+      </c>
+      <c r="B480" t="s">
+        <v>7</v>
+      </c>
+      <c r="C480" t="s">
+        <v>8</v>
+      </c>
+      <c r="D480" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A481">
+        <v>741</v>
+      </c>
+      <c r="B481" t="s">
+        <v>7</v>
+      </c>
+      <c r="C481" t="s">
+        <v>8</v>
+      </c>
+      <c r="D481" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>742</v>
+      </c>
+      <c r="B482" t="s">
+        <v>7</v>
+      </c>
+      <c r="C482" t="s">
+        <v>8</v>
+      </c>
+      <c r="D482" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A483">
+        <v>743</v>
+      </c>
+      <c r="B483" t="s">
+        <v>7</v>
+      </c>
+      <c r="C483" t="s">
+        <v>8</v>
+      </c>
+      <c r="D483" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>744</v>
+      </c>
+      <c r="B484" t="s">
+        <v>7</v>
+      </c>
+      <c r="C484" t="s">
+        <v>8</v>
+      </c>
+      <c r="D484" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A485">
+        <v>745</v>
+      </c>
+      <c r="B485" t="s">
+        <v>7</v>
+      </c>
+      <c r="C485" t="s">
+        <v>8</v>
+      </c>
+      <c r="D485" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A486">
+        <v>746</v>
+      </c>
+      <c r="B486" t="s">
+        <v>7</v>
+      </c>
+      <c r="C486" t="s">
+        <v>8</v>
+      </c>
+      <c r="D486" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A487">
+        <v>747</v>
+      </c>
+      <c r="B487" t="s">
+        <v>4</v>
+      </c>
+      <c r="C487" t="s">
+        <v>5</v>
+      </c>
+      <c r="D487" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A488">
+        <v>748</v>
+      </c>
+      <c r="B488" t="s">
+        <v>7</v>
+      </c>
+      <c r="C488" t="s">
+        <v>8</v>
+      </c>
+      <c r="D488" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A489">
+        <v>749</v>
+      </c>
+      <c r="B489" t="s">
+        <v>4</v>
+      </c>
+      <c r="C489" t="s">
+        <v>5</v>
+      </c>
+      <c r="D489" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A490">
+        <v>750</v>
+      </c>
+      <c r="B490" t="s">
+        <v>4</v>
+      </c>
+      <c r="C490" t="s">
+        <v>5</v>
+      </c>
+      <c r="D490" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A491">
+        <v>751</v>
+      </c>
+      <c r="B491" t="s">
+        <v>4</v>
+      </c>
+      <c r="C491" t="s">
+        <v>5</v>
+      </c>
+      <c r="D491" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A492">
+        <v>752</v>
+      </c>
+      <c r="B492" t="s">
+        <v>4</v>
+      </c>
+      <c r="C492" t="s">
+        <v>5</v>
+      </c>
+      <c r="D492" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A493">
+        <v>753</v>
+      </c>
+      <c r="B493" t="s">
+        <v>4</v>
+      </c>
+      <c r="C493" t="s">
+        <v>5</v>
+      </c>
+      <c r="D493" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A494">
+        <v>754</v>
+      </c>
+      <c r="B494" t="s">
+        <v>4</v>
+      </c>
+      <c r="C494" t="s">
+        <v>5</v>
+      </c>
+      <c r="D494" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A495">
+        <v>755</v>
+      </c>
+      <c r="B495" t="s">
+        <v>4</v>
+      </c>
+      <c r="C495" t="s">
+        <v>5</v>
+      </c>
+      <c r="D495" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A496">
+        <v>756</v>
+      </c>
+      <c r="B496" t="s">
+        <v>4</v>
+      </c>
+      <c r="C496" t="s">
+        <v>5</v>
+      </c>
+      <c r="D496" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A497">
+        <v>757</v>
+      </c>
+      <c r="B497" t="s">
+        <v>4</v>
+      </c>
+      <c r="C497" t="s">
+        <v>5</v>
+      </c>
+      <c r="D497" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A498">
+        <v>758</v>
+      </c>
+      <c r="B498" t="s">
+        <v>4</v>
+      </c>
+      <c r="C498" t="s">
+        <v>5</v>
+      </c>
+      <c r="D498" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A499">
+        <v>759</v>
+      </c>
+      <c r="B499" t="s">
+        <v>4</v>
+      </c>
+      <c r="C499" t="s">
+        <v>5</v>
+      </c>
+      <c r="D499" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500">
+        <v>760</v>
+      </c>
+      <c r="B500" t="s">
+        <v>4</v>
+      </c>
+      <c r="C500" t="s">
+        <v>5</v>
+      </c>
+      <c r="D500" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501">
+        <v>761</v>
+      </c>
+      <c r="B501" t="s">
+        <v>4</v>
+      </c>
+      <c r="C501" t="s">
+        <v>5</v>
+      </c>
+      <c r="D501" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502">
+        <v>762</v>
+      </c>
+      <c r="B502" t="s">
+        <v>4</v>
+      </c>
+      <c r="C502" t="s">
+        <v>5</v>
+      </c>
+      <c r="D502" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503">
+        <v>763</v>
+      </c>
+      <c r="B503" t="s">
+        <v>7</v>
+      </c>
+      <c r="C503" t="s">
+        <v>8</v>
+      </c>
+      <c r="D503" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504">
+        <v>764</v>
+      </c>
+      <c r="B504" t="s">
+        <v>4</v>
+      </c>
+      <c r="C504" t="s">
+        <v>5</v>
+      </c>
+      <c r="D504" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505">
+        <v>765</v>
+      </c>
+      <c r="B505" t="s">
+        <v>4</v>
+      </c>
+      <c r="C505" t="s">
+        <v>5</v>
+      </c>
+      <c r="D505" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506">
+        <v>766</v>
+      </c>
+      <c r="B506" t="s">
+        <v>4</v>
+      </c>
+      <c r="C506" t="s">
+        <v>5</v>
+      </c>
+      <c r="D506" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A507">
+        <v>767</v>
+      </c>
+      <c r="B507" t="s">
+        <v>4</v>
+      </c>
+      <c r="C507" t="s">
+        <v>5</v>
+      </c>
+      <c r="D507" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A508">
+        <v>768</v>
+      </c>
+      <c r="B508" t="s">
+        <v>7</v>
+      </c>
+      <c r="C508" t="s">
+        <v>8</v>
+      </c>
+      <c r="D508" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A509">
+        <v>769</v>
+      </c>
+      <c r="B509" t="s">
+        <v>4</v>
+      </c>
+      <c r="C509" t="s">
+        <v>5</v>
+      </c>
+      <c r="D509" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A510">
+        <v>770</v>
+      </c>
+      <c r="B510" t="s">
+        <v>7</v>
+      </c>
+      <c r="C510" t="s">
+        <v>8</v>
+      </c>
+      <c r="D510" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A511">
+        <v>771</v>
+      </c>
+      <c r="B511" t="s">
+        <v>4</v>
+      </c>
+      <c r="C511" t="s">
+        <v>5</v>
+      </c>
+      <c r="D511" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A512">
+        <v>772</v>
+      </c>
+      <c r="B512" t="s">
+        <v>4</v>
+      </c>
+      <c r="C512" t="s">
+        <v>5</v>
+      </c>
+      <c r="D512" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A513">
+        <v>773</v>
+      </c>
+      <c r="B513" t="s">
+        <v>4</v>
+      </c>
+      <c r="C513" t="s">
+        <v>5</v>
+      </c>
+      <c r="D513" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A514">
+        <v>774</v>
+      </c>
+      <c r="B514" t="s">
+        <v>4</v>
+      </c>
+      <c r="C514" t="s">
+        <v>5</v>
+      </c>
+      <c r="D514" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A515">
+        <v>775</v>
+      </c>
+      <c r="B515" t="s">
+        <v>4</v>
+      </c>
+      <c r="C515" t="s">
+        <v>5</v>
+      </c>
+      <c r="D515" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A516">
+        <v>776</v>
+      </c>
+      <c r="B516" t="s">
+        <v>4</v>
+      </c>
+      <c r="C516" t="s">
+        <v>5</v>
+      </c>
+      <c r="D516" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A517">
+        <v>777</v>
+      </c>
+      <c r="B517" t="s">
+        <v>4</v>
+      </c>
+      <c r="C517" t="s">
+        <v>5</v>
+      </c>
+      <c r="D517" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A518">
+        <v>778</v>
+      </c>
+      <c r="B518" t="s">
+        <v>4</v>
+      </c>
+      <c r="C518" t="s">
+        <v>5</v>
+      </c>
+      <c r="D518" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A519">
+        <v>779</v>
+      </c>
+      <c r="B519" t="s">
+        <v>4</v>
+      </c>
+      <c r="C519" t="s">
+        <v>5</v>
+      </c>
+      <c r="D519" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A520">
+        <v>780</v>
+      </c>
+      <c r="B520" t="s">
+        <v>4</v>
+      </c>
+      <c r="C520" t="s">
+        <v>5</v>
+      </c>
+      <c r="D520" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A521">
+        <v>781</v>
+      </c>
+      <c r="B521" t="s">
+        <v>4</v>
+      </c>
+      <c r="C521" t="s">
+        <v>5</v>
+      </c>
+      <c r="D521" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A522">
+        <v>782</v>
+      </c>
+      <c r="B522" t="s">
+        <v>4</v>
+      </c>
+      <c r="C522" t="s">
+        <v>5</v>
+      </c>
+      <c r="D522" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A523">
+        <v>783</v>
+      </c>
+      <c r="B523" t="s">
+        <v>4</v>
+      </c>
+      <c r="C523" t="s">
+        <v>5</v>
+      </c>
+      <c r="D523" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A524">
+        <v>784</v>
+      </c>
+      <c r="B524" t="s">
+        <v>4</v>
+      </c>
+      <c r="C524" t="s">
+        <v>5</v>
+      </c>
+      <c r="D524" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A525">
+        <v>785</v>
+      </c>
+      <c r="B525" t="s">
+        <v>4</v>
+      </c>
+      <c r="C525" t="s">
+        <v>5</v>
+      </c>
+      <c r="D525" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A526">
+        <v>786</v>
+      </c>
+      <c r="B526" t="s">
+        <v>4</v>
+      </c>
+      <c r="C526" t="s">
+        <v>5</v>
+      </c>
+      <c r="D526" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A527">
+        <v>787</v>
+      </c>
+      <c r="B527" t="s">
+        <v>4</v>
+      </c>
+      <c r="C527" t="s">
+        <v>5</v>
+      </c>
+      <c r="D527" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A528">
+        <v>788</v>
+      </c>
+      <c r="B528" t="s">
+        <v>4</v>
+      </c>
+      <c r="C528" t="s">
+        <v>5</v>
+      </c>
+      <c r="D528" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A529">
+        <v>789</v>
+      </c>
+      <c r="B529" t="s">
+        <v>4</v>
+      </c>
+      <c r="C529" t="s">
+        <v>5</v>
+      </c>
+      <c r="D529" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A530">
+        <v>790</v>
+      </c>
+      <c r="B530" t="s">
+        <v>4</v>
+      </c>
+      <c r="C530" t="s">
+        <v>5</v>
+      </c>
+      <c r="D530" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A531">
+        <v>791</v>
+      </c>
+      <c r="B531" t="s">
+        <v>7</v>
+      </c>
+      <c r="C531" t="s">
+        <v>8</v>
+      </c>
+      <c r="D531" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A532">
+        <v>792</v>
+      </c>
+      <c r="B532" t="s">
+        <v>4</v>
+      </c>
+      <c r="C532" t="s">
+        <v>5</v>
+      </c>
+      <c r="D532" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A533">
+        <v>793</v>
+      </c>
+      <c r="B533" t="s">
+        <v>7</v>
+      </c>
+      <c r="C533" t="s">
+        <v>8</v>
+      </c>
+      <c r="D533" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A534">
+        <v>794</v>
+      </c>
+      <c r="B534" t="s">
+        <v>4</v>
+      </c>
+      <c r="C534" t="s">
+        <v>5</v>
+      </c>
+      <c r="D534" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A535">
+        <v>795</v>
+      </c>
+      <c r="B535" t="s">
+        <v>4</v>
+      </c>
+      <c r="C535" t="s">
+        <v>5</v>
+      </c>
+      <c r="D535" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A536">
+        <v>796</v>
+      </c>
+      <c r="B536" t="s">
+        <v>4</v>
+      </c>
+      <c r="C536" t="s">
+        <v>5</v>
+      </c>
+      <c r="D536" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A537">
+        <v>797</v>
+      </c>
+      <c r="B537" t="s">
+        <v>4</v>
+      </c>
+      <c r="C537" t="s">
+        <v>5</v>
+      </c>
+      <c r="D537" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A538">
+        <v>798</v>
+      </c>
+      <c r="B538" t="s">
+        <v>4</v>
+      </c>
+      <c r="C538" t="s">
+        <v>5</v>
+      </c>
+      <c r="D538" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A539">
+        <v>799</v>
+      </c>
+      <c r="B539" t="s">
+        <v>7</v>
+      </c>
+      <c r="C539" t="s">
+        <v>8</v>
+      </c>
+      <c r="D539" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A540">
+        <v>800</v>
+      </c>
+      <c r="B540" t="s">
+        <v>4</v>
+      </c>
+      <c r="C540" t="s">
+        <v>5</v>
+      </c>
+      <c r="D540" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A541">
+        <v>801</v>
+      </c>
+      <c r="B541" t="s">
+        <v>4</v>
+      </c>
+      <c r="C541" t="s">
+        <v>5</v>
+      </c>
+      <c r="D541" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A542">
+        <v>802</v>
+      </c>
+      <c r="B542" t="s">
+        <v>4</v>
+      </c>
+      <c r="C542" t="s">
+        <v>5</v>
+      </c>
+      <c r="D542" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A543">
+        <v>803</v>
+      </c>
+      <c r="B543" t="s">
+        <v>4</v>
+      </c>
+      <c r="C543" t="s">
+        <v>5</v>
+      </c>
+      <c r="D543" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A544">
+        <v>804</v>
+      </c>
+      <c r="B544" t="s">
+        <v>4</v>
+      </c>
+      <c r="C544" t="s">
+        <v>5</v>
+      </c>
+      <c r="D544" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A545">
+        <v>805</v>
+      </c>
+      <c r="B545" t="s">
+        <v>4</v>
+      </c>
+      <c r="C545" t="s">
+        <v>5</v>
+      </c>
+      <c r="D545" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A546">
+        <v>806</v>
+      </c>
+      <c r="B546" t="s">
+        <v>4</v>
+      </c>
+      <c r="C546" t="s">
+        <v>5</v>
+      </c>
+      <c r="D546" t="s">
+        <v>552</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/backend/excel-data/holidaystudentsub_library_migration.xlsx
+++ b/apps/backend/excel-data/holidaystudentsub_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="667">
   <si>
     <t>legacy_id</t>
   </si>
@@ -1670,6 +1670,348 @@
   </si>
   <si>
     <t>2026-06-20T07:51:52.367Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:53.703Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:55.160Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:56.709Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:58.299Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:51:59.602Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:00.980Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:02.072Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:03.597Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:05.186Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:06.825Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:09.054Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:10.605Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:12.741Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:14.070Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:15.425Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:16.945Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:18.506Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:20.092Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:22.140Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:23.707Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:26.019Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:29.795Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:32.160Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:34.325Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:37.425Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:40.211Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:41.924Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:43.386Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:45.219Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:46.647Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:47.845Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:49.616Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:51.191Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:52.683Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:54.003Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:55.548Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:57.080Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:52:59.045Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:00.822Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:02.223Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:03.435Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:04.714Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:06.613Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:08.256Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:09.591Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:11.014Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:12.171Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:13.400Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:15.118Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:16.433Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:17.570Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:18.692Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:19.832Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:21.197Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:22.276Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:23.303Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:24.369Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:25.434Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:26.498Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:27.709Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:28.724Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:29.687Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:30.650Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:32.193Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:33.465Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:34.515Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:35.587Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:36.791Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:37.822Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:39.308Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:40.384Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:41.965Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:43.356Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:44.796Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:46.411Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:47.876Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:49.217Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:50.663Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:52.661Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:54.409Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:55.852Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:57.339Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:53:59.035Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:00.545Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:01.916Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:03.027Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:04.575Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:05.998Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:07.521Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:08.868Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:10.119Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:11.414Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:12.490Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:13.832Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:15.387Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:16.838Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:18.238Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:19.563Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:20.998Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:22.595Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:23.968Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:25.458Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:26.778Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:28.316Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:29.581Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:30.860Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:32.127Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:33.863Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:35.383Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:36.626Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:37.926Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:39.267Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:40.844Z</t>
+  </si>
+  <si>
+    <t>2026-06-20T07:54:41.873Z</t>
   </si>
 </sst>
 </file>
@@ -2050,7 +2392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D546"/>
+  <dimension ref="A1:D660"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -9697,6 +10039,1602 @@
         <v>552</v>
       </c>
     </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A547">
+        <v>807</v>
+      </c>
+      <c r="B547" t="s">
+        <v>4</v>
+      </c>
+      <c r="C547" t="s">
+        <v>5</v>
+      </c>
+      <c r="D547" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A548">
+        <v>808</v>
+      </c>
+      <c r="B548" t="s">
+        <v>4</v>
+      </c>
+      <c r="C548" t="s">
+        <v>5</v>
+      </c>
+      <c r="D548" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A549">
+        <v>809</v>
+      </c>
+      <c r="B549" t="s">
+        <v>4</v>
+      </c>
+      <c r="C549" t="s">
+        <v>5</v>
+      </c>
+      <c r="D549" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A550">
+        <v>810</v>
+      </c>
+      <c r="B550" t="s">
+        <v>4</v>
+      </c>
+      <c r="C550" t="s">
+        <v>5</v>
+      </c>
+      <c r="D550" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A551">
+        <v>811</v>
+      </c>
+      <c r="B551" t="s">
+        <v>4</v>
+      </c>
+      <c r="C551" t="s">
+        <v>5</v>
+      </c>
+      <c r="D551" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A552">
+        <v>812</v>
+      </c>
+      <c r="B552" t="s">
+        <v>4</v>
+      </c>
+      <c r="C552" t="s">
+        <v>5</v>
+      </c>
+      <c r="D552" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A553">
+        <v>813</v>
+      </c>
+      <c r="B553" t="s">
+        <v>7</v>
+      </c>
+      <c r="C553" t="s">
+        <v>8</v>
+      </c>
+      <c r="D553" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A554">
+        <v>814</v>
+      </c>
+      <c r="B554" t="s">
+        <v>4</v>
+      </c>
+      <c r="C554" t="s">
+        <v>5</v>
+      </c>
+      <c r="D554" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A555">
+        <v>815</v>
+      </c>
+      <c r="B555" t="s">
+        <v>4</v>
+      </c>
+      <c r="C555" t="s">
+        <v>5</v>
+      </c>
+      <c r="D555" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A556">
+        <v>816</v>
+      </c>
+      <c r="B556" t="s">
+        <v>4</v>
+      </c>
+      <c r="C556" t="s">
+        <v>5</v>
+      </c>
+      <c r="D556" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A557">
+        <v>817</v>
+      </c>
+      <c r="B557" t="s">
+        <v>4</v>
+      </c>
+      <c r="C557" t="s">
+        <v>5</v>
+      </c>
+      <c r="D557" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A558">
+        <v>818</v>
+      </c>
+      <c r="B558" t="s">
+        <v>7</v>
+      </c>
+      <c r="C558" t="s">
+        <v>8</v>
+      </c>
+      <c r="D558" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A559">
+        <v>819</v>
+      </c>
+      <c r="B559" t="s">
+        <v>4</v>
+      </c>
+      <c r="C559" t="s">
+        <v>5</v>
+      </c>
+      <c r="D559" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A560">
+        <v>820</v>
+      </c>
+      <c r="B560" t="s">
+        <v>7</v>
+      </c>
+      <c r="C560" t="s">
+        <v>8</v>
+      </c>
+      <c r="D560" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A561">
+        <v>821</v>
+      </c>
+      <c r="B561" t="s">
+        <v>4</v>
+      </c>
+      <c r="C561" t="s">
+        <v>5</v>
+      </c>
+      <c r="D561" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A562">
+        <v>822</v>
+      </c>
+      <c r="B562" t="s">
+        <v>4</v>
+      </c>
+      <c r="C562" t="s">
+        <v>5</v>
+      </c>
+      <c r="D562" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A563">
+        <v>823</v>
+      </c>
+      <c r="B563" t="s">
+        <v>4</v>
+      </c>
+      <c r="C563" t="s">
+        <v>5</v>
+      </c>
+      <c r="D563" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A564">
+        <v>824</v>
+      </c>
+      <c r="B564" t="s">
+        <v>4</v>
+      </c>
+      <c r="C564" t="s">
+        <v>5</v>
+      </c>
+      <c r="D564" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A565">
+        <v>825</v>
+      </c>
+      <c r="B565" t="s">
+        <v>4</v>
+      </c>
+      <c r="C565" t="s">
+        <v>5</v>
+      </c>
+      <c r="D565" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A566">
+        <v>826</v>
+      </c>
+      <c r="B566" t="s">
+        <v>4</v>
+      </c>
+      <c r="C566" t="s">
+        <v>5</v>
+      </c>
+      <c r="D566" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A567">
+        <v>827</v>
+      </c>
+      <c r="B567" t="s">
+        <v>4</v>
+      </c>
+      <c r="C567" t="s">
+        <v>5</v>
+      </c>
+      <c r="D567" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A568">
+        <v>828</v>
+      </c>
+      <c r="B568" t="s">
+        <v>4</v>
+      </c>
+      <c r="C568" t="s">
+        <v>5</v>
+      </c>
+      <c r="D568" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A569">
+        <v>829</v>
+      </c>
+      <c r="B569" t="s">
+        <v>4</v>
+      </c>
+      <c r="C569" t="s">
+        <v>5</v>
+      </c>
+      <c r="D569" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A570">
+        <v>830</v>
+      </c>
+      <c r="B570" t="s">
+        <v>4</v>
+      </c>
+      <c r="C570" t="s">
+        <v>5</v>
+      </c>
+      <c r="D570" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A571">
+        <v>831</v>
+      </c>
+      <c r="B571" t="s">
+        <v>4</v>
+      </c>
+      <c r="C571" t="s">
+        <v>5</v>
+      </c>
+      <c r="D571" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A572">
+        <v>832</v>
+      </c>
+      <c r="B572" t="s">
+        <v>4</v>
+      </c>
+      <c r="C572" t="s">
+        <v>5</v>
+      </c>
+      <c r="D572" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A573">
+        <v>833</v>
+      </c>
+      <c r="B573" t="s">
+        <v>4</v>
+      </c>
+      <c r="C573" t="s">
+        <v>5</v>
+      </c>
+      <c r="D573" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A574">
+        <v>834</v>
+      </c>
+      <c r="B574" t="s">
+        <v>4</v>
+      </c>
+      <c r="C574" t="s">
+        <v>5</v>
+      </c>
+      <c r="D574" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A575">
+        <v>835</v>
+      </c>
+      <c r="B575" t="s">
+        <v>4</v>
+      </c>
+      <c r="C575" t="s">
+        <v>5</v>
+      </c>
+      <c r="D575" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A576">
+        <v>836</v>
+      </c>
+      <c r="B576" t="s">
+        <v>4</v>
+      </c>
+      <c r="C576" t="s">
+        <v>5</v>
+      </c>
+      <c r="D576" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A577">
+        <v>837</v>
+      </c>
+      <c r="B577" t="s">
+        <v>7</v>
+      </c>
+      <c r="C577" t="s">
+        <v>8</v>
+      </c>
+      <c r="D577" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A578">
+        <v>838</v>
+      </c>
+      <c r="B578" t="s">
+        <v>4</v>
+      </c>
+      <c r="C578" t="s">
+        <v>5</v>
+      </c>
+      <c r="D578" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A579">
+        <v>839</v>
+      </c>
+      <c r="B579" t="s">
+        <v>7</v>
+      </c>
+      <c r="C579" t="s">
+        <v>8</v>
+      </c>
+      <c r="D579" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A580">
+        <v>840</v>
+      </c>
+      <c r="B580" t="s">
+        <v>4</v>
+      </c>
+      <c r="C580" t="s">
+        <v>5</v>
+      </c>
+      <c r="D580" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A581">
+        <v>841</v>
+      </c>
+      <c r="B581" t="s">
+        <v>4</v>
+      </c>
+      <c r="C581" t="s">
+        <v>5</v>
+      </c>
+      <c r="D581" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A582">
+        <v>842</v>
+      </c>
+      <c r="B582" t="s">
+        <v>4</v>
+      </c>
+      <c r="C582" t="s">
+        <v>5</v>
+      </c>
+      <c r="D582" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A583">
+        <v>843</v>
+      </c>
+      <c r="B583" t="s">
+        <v>4</v>
+      </c>
+      <c r="C583" t="s">
+        <v>5</v>
+      </c>
+      <c r="D583" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A584">
+        <v>844</v>
+      </c>
+      <c r="B584" t="s">
+        <v>7</v>
+      </c>
+      <c r="C584" t="s">
+        <v>8</v>
+      </c>
+      <c r="D584" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A585">
+        <v>845</v>
+      </c>
+      <c r="B585" t="s">
+        <v>7</v>
+      </c>
+      <c r="C585" t="s">
+        <v>8</v>
+      </c>
+      <c r="D585" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A586">
+        <v>846</v>
+      </c>
+      <c r="B586" t="s">
+        <v>7</v>
+      </c>
+      <c r="C586" t="s">
+        <v>8</v>
+      </c>
+      <c r="D586" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A587">
+        <v>847</v>
+      </c>
+      <c r="B587" t="s">
+        <v>7</v>
+      </c>
+      <c r="C587" t="s">
+        <v>8</v>
+      </c>
+      <c r="D587" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A588">
+        <v>848</v>
+      </c>
+      <c r="B588" t="s">
+        <v>7</v>
+      </c>
+      <c r="C588" t="s">
+        <v>8</v>
+      </c>
+      <c r="D588" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A589">
+        <v>849</v>
+      </c>
+      <c r="B589" t="s">
+        <v>7</v>
+      </c>
+      <c r="C589" t="s">
+        <v>8</v>
+      </c>
+      <c r="D589" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A590">
+        <v>850</v>
+      </c>
+      <c r="B590" t="s">
+        <v>7</v>
+      </c>
+      <c r="C590" t="s">
+        <v>8</v>
+      </c>
+      <c r="D590" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A591">
+        <v>851</v>
+      </c>
+      <c r="B591" t="s">
+        <v>7</v>
+      </c>
+      <c r="C591" t="s">
+        <v>8</v>
+      </c>
+      <c r="D591" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A592">
+        <v>852</v>
+      </c>
+      <c r="B592" t="s">
+        <v>7</v>
+      </c>
+      <c r="C592" t="s">
+        <v>8</v>
+      </c>
+      <c r="D592" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A593">
+        <v>853</v>
+      </c>
+      <c r="B593" t="s">
+        <v>7</v>
+      </c>
+      <c r="C593" t="s">
+        <v>8</v>
+      </c>
+      <c r="D593" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A594">
+        <v>854</v>
+      </c>
+      <c r="B594" t="s">
+        <v>7</v>
+      </c>
+      <c r="C594" t="s">
+        <v>8</v>
+      </c>
+      <c r="D594" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A595">
+        <v>855</v>
+      </c>
+      <c r="B595" t="s">
+        <v>7</v>
+      </c>
+      <c r="C595" t="s">
+        <v>8</v>
+      </c>
+      <c r="D595" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A596">
+        <v>856</v>
+      </c>
+      <c r="B596" t="s">
+        <v>7</v>
+      </c>
+      <c r="C596" t="s">
+        <v>8</v>
+      </c>
+      <c r="D596" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A597">
+        <v>857</v>
+      </c>
+      <c r="B597" t="s">
+        <v>7</v>
+      </c>
+      <c r="C597" t="s">
+        <v>8</v>
+      </c>
+      <c r="D597" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A598">
+        <v>858</v>
+      </c>
+      <c r="B598" t="s">
+        <v>7</v>
+      </c>
+      <c r="C598" t="s">
+        <v>8</v>
+      </c>
+      <c r="D598" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A599">
+        <v>859</v>
+      </c>
+      <c r="B599" t="s">
+        <v>7</v>
+      </c>
+      <c r="C599" t="s">
+        <v>8</v>
+      </c>
+      <c r="D599" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A600">
+        <v>860</v>
+      </c>
+      <c r="B600" t="s">
+        <v>7</v>
+      </c>
+      <c r="C600" t="s">
+        <v>8</v>
+      </c>
+      <c r="D600" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A601">
+        <v>861</v>
+      </c>
+      <c r="B601" t="s">
+        <v>7</v>
+      </c>
+      <c r="C601" t="s">
+        <v>8</v>
+      </c>
+      <c r="D601" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A602">
+        <v>862</v>
+      </c>
+      <c r="B602" t="s">
+        <v>7</v>
+      </c>
+      <c r="C602" t="s">
+        <v>8</v>
+      </c>
+      <c r="D602" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A603">
+        <v>863</v>
+      </c>
+      <c r="B603" t="s">
+        <v>7</v>
+      </c>
+      <c r="C603" t="s">
+        <v>8</v>
+      </c>
+      <c r="D603" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A604">
+        <v>864</v>
+      </c>
+      <c r="B604" t="s">
+        <v>7</v>
+      </c>
+      <c r="C604" t="s">
+        <v>8</v>
+      </c>
+      <c r="D604" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A605">
+        <v>865</v>
+      </c>
+      <c r="B605" t="s">
+        <v>7</v>
+      </c>
+      <c r="C605" t="s">
+        <v>8</v>
+      </c>
+      <c r="D605" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A606">
+        <v>866</v>
+      </c>
+      <c r="B606" t="s">
+        <v>7</v>
+      </c>
+      <c r="C606" t="s">
+        <v>8</v>
+      </c>
+      <c r="D606" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A607">
+        <v>867</v>
+      </c>
+      <c r="B607" t="s">
+        <v>7</v>
+      </c>
+      <c r="C607" t="s">
+        <v>8</v>
+      </c>
+      <c r="D607" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A608">
+        <v>868</v>
+      </c>
+      <c r="B608" t="s">
+        <v>7</v>
+      </c>
+      <c r="C608" t="s">
+        <v>8</v>
+      </c>
+      <c r="D608" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A609">
+        <v>869</v>
+      </c>
+      <c r="B609" t="s">
+        <v>7</v>
+      </c>
+      <c r="C609" t="s">
+        <v>8</v>
+      </c>
+      <c r="D609" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A610">
+        <v>870</v>
+      </c>
+      <c r="B610" t="s">
+        <v>7</v>
+      </c>
+      <c r="C610" t="s">
+        <v>8</v>
+      </c>
+      <c r="D610" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A611">
+        <v>871</v>
+      </c>
+      <c r="B611" t="s">
+        <v>7</v>
+      </c>
+      <c r="C611" t="s">
+        <v>8</v>
+      </c>
+      <c r="D611" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A612">
+        <v>872</v>
+      </c>
+      <c r="B612" t="s">
+        <v>7</v>
+      </c>
+      <c r="C612" t="s">
+        <v>8</v>
+      </c>
+      <c r="D612" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A613">
+        <v>873</v>
+      </c>
+      <c r="B613" t="s">
+        <v>7</v>
+      </c>
+      <c r="C613" t="s">
+        <v>8</v>
+      </c>
+      <c r="D613" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A614">
+        <v>874</v>
+      </c>
+      <c r="B614" t="s">
+        <v>7</v>
+      </c>
+      <c r="C614" t="s">
+        <v>8</v>
+      </c>
+      <c r="D614" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A615">
+        <v>875</v>
+      </c>
+      <c r="B615" t="s">
+        <v>7</v>
+      </c>
+      <c r="C615" t="s">
+        <v>8</v>
+      </c>
+      <c r="D615" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A616">
+        <v>876</v>
+      </c>
+      <c r="B616" t="s">
+        <v>4</v>
+      </c>
+      <c r="C616" t="s">
+        <v>5</v>
+      </c>
+      <c r="D616" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A617">
+        <v>877</v>
+      </c>
+      <c r="B617" t="s">
+        <v>7</v>
+      </c>
+      <c r="C617" t="s">
+        <v>8</v>
+      </c>
+      <c r="D617" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A618">
+        <v>878</v>
+      </c>
+      <c r="B618" t="s">
+        <v>4</v>
+      </c>
+      <c r="C618" t="s">
+        <v>5</v>
+      </c>
+      <c r="D618" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A619">
+        <v>879</v>
+      </c>
+      <c r="B619" t="s">
+        <v>4</v>
+      </c>
+      <c r="C619" t="s">
+        <v>5</v>
+      </c>
+      <c r="D619" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A620">
+        <v>880</v>
+      </c>
+      <c r="B620" t="s">
+        <v>4</v>
+      </c>
+      <c r="C620" t="s">
+        <v>5</v>
+      </c>
+      <c r="D620" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A621">
+        <v>881</v>
+      </c>
+      <c r="B621" t="s">
+        <v>4</v>
+      </c>
+      <c r="C621" t="s">
+        <v>5</v>
+      </c>
+      <c r="D621" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A622">
+        <v>882</v>
+      </c>
+      <c r="B622" t="s">
+        <v>4</v>
+      </c>
+      <c r="C622" t="s">
+        <v>5</v>
+      </c>
+      <c r="D622" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A623">
+        <v>883</v>
+      </c>
+      <c r="B623" t="s">
+        <v>4</v>
+      </c>
+      <c r="C623" t="s">
+        <v>5</v>
+      </c>
+      <c r="D623" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A624">
+        <v>884</v>
+      </c>
+      <c r="B624" t="s">
+        <v>4</v>
+      </c>
+      <c r="C624" t="s">
+        <v>5</v>
+      </c>
+      <c r="D624" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A625">
+        <v>885</v>
+      </c>
+      <c r="B625" t="s">
+        <v>4</v>
+      </c>
+      <c r="C625" t="s">
+        <v>5</v>
+      </c>
+      <c r="D625" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A626">
+        <v>886</v>
+      </c>
+      <c r="B626" t="s">
+        <v>4</v>
+      </c>
+      <c r="C626" t="s">
+        <v>5</v>
+      </c>
+      <c r="D626" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A627">
+        <v>887</v>
+      </c>
+      <c r="B627" t="s">
+        <v>4</v>
+      </c>
+      <c r="C627" t="s">
+        <v>5</v>
+      </c>
+      <c r="D627" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A628">
+        <v>888</v>
+      </c>
+      <c r="B628" t="s">
+        <v>4</v>
+      </c>
+      <c r="C628" t="s">
+        <v>5</v>
+      </c>
+      <c r="D628" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A629">
+        <v>889</v>
+      </c>
+      <c r="B629" t="s">
+        <v>4</v>
+      </c>
+      <c r="C629" t="s">
+        <v>5</v>
+      </c>
+      <c r="D629" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A630">
+        <v>890</v>
+      </c>
+      <c r="B630" t="s">
+        <v>4</v>
+      </c>
+      <c r="C630" t="s">
+        <v>5</v>
+      </c>
+      <c r="D630" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A631">
+        <v>891</v>
+      </c>
+      <c r="B631" t="s">
+        <v>4</v>
+      </c>
+      <c r="C631" t="s">
+        <v>5</v>
+      </c>
+      <c r="D631" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A632">
+        <v>892</v>
+      </c>
+      <c r="B632" t="s">
+        <v>7</v>
+      </c>
+      <c r="C632" t="s">
+        <v>8</v>
+      </c>
+      <c r="D632" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A633">
+        <v>893</v>
+      </c>
+      <c r="B633" t="s">
+        <v>4</v>
+      </c>
+      <c r="C633" t="s">
+        <v>5</v>
+      </c>
+      <c r="D633" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A634">
+        <v>894</v>
+      </c>
+      <c r="B634" t="s">
+        <v>4</v>
+      </c>
+      <c r="C634" t="s">
+        <v>5</v>
+      </c>
+      <c r="D634" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A635">
+        <v>895</v>
+      </c>
+      <c r="B635" t="s">
+        <v>4</v>
+      </c>
+      <c r="C635" t="s">
+        <v>5</v>
+      </c>
+      <c r="D635" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A636">
+        <v>896</v>
+      </c>
+      <c r="B636" t="s">
+        <v>4</v>
+      </c>
+      <c r="C636" t="s">
+        <v>5</v>
+      </c>
+      <c r="D636" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A637">
+        <v>897</v>
+      </c>
+      <c r="B637" t="s">
+        <v>7</v>
+      </c>
+      <c r="C637" t="s">
+        <v>8</v>
+      </c>
+      <c r="D637" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A638">
+        <v>898</v>
+      </c>
+      <c r="B638" t="s">
+        <v>4</v>
+      </c>
+      <c r="C638" t="s">
+        <v>5</v>
+      </c>
+      <c r="D638" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A639">
+        <v>899</v>
+      </c>
+      <c r="B639" t="s">
+        <v>7</v>
+      </c>
+      <c r="C639" t="s">
+        <v>8</v>
+      </c>
+      <c r="D639" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A640">
+        <v>900</v>
+      </c>
+      <c r="B640" t="s">
+        <v>4</v>
+      </c>
+      <c r="C640" t="s">
+        <v>5</v>
+      </c>
+      <c r="D640" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A641">
+        <v>901</v>
+      </c>
+      <c r="B641" t="s">
+        <v>4</v>
+      </c>
+      <c r="C641" t="s">
+        <v>5</v>
+      </c>
+      <c r="D641" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A642">
+        <v>902</v>
+      </c>
+      <c r="B642" t="s">
+        <v>4</v>
+      </c>
+      <c r="C642" t="s">
+        <v>5</v>
+      </c>
+      <c r="D642" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A643">
+        <v>903</v>
+      </c>
+      <c r="B643" t="s">
+        <v>4</v>
+      </c>
+      <c r="C643" t="s">
+        <v>5</v>
+      </c>
+      <c r="D643" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A644">
+        <v>904</v>
+      </c>
+      <c r="B644" t="s">
+        <v>4</v>
+      </c>
+      <c r="C644" t="s">
+        <v>5</v>
+      </c>
+      <c r="D644" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A645">
+        <v>905</v>
+      </c>
+      <c r="B645" t="s">
+        <v>4</v>
+      </c>
+      <c r="C645" t="s">
+        <v>5</v>
+      </c>
+      <c r="D645" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A646">
+        <v>906</v>
+      </c>
+      <c r="B646" t="s">
+        <v>4</v>
+      </c>
+      <c r="C646" t="s">
+        <v>5</v>
+      </c>
+      <c r="D646" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A647">
+        <v>907</v>
+      </c>
+      <c r="B647" t="s">
+        <v>4</v>
+      </c>
+      <c r="C647" t="s">
+        <v>5</v>
+      </c>
+      <c r="D647" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A648">
+        <v>908</v>
+      </c>
+      <c r="B648" t="s">
+        <v>4</v>
+      </c>
+      <c r="C648" t="s">
+        <v>5</v>
+      </c>
+      <c r="D648" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A649">
+        <v>909</v>
+      </c>
+      <c r="B649" t="s">
+        <v>4</v>
+      </c>
+      <c r="C649" t="s">
+        <v>5</v>
+      </c>
+      <c r="D649" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A650">
+        <v>910</v>
+      </c>
+      <c r="B650" t="s">
+        <v>4</v>
+      </c>
+      <c r="C650" t="s">
+        <v>5</v>
+      </c>
+      <c r="D650" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A651">
+        <v>911</v>
+      </c>
+      <c r="B651" t="s">
+        <v>4</v>
+      </c>
+      <c r="C651" t="s">
+        <v>5</v>
+      </c>
+      <c r="D651" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A652">
+        <v>912</v>
+      </c>
+      <c r="B652" t="s">
+        <v>4</v>
+      </c>
+      <c r="C652" t="s">
+        <v>5</v>
+      </c>
+      <c r="D652" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A653">
+        <v>913</v>
+      </c>
+      <c r="B653" t="s">
+        <v>4</v>
+      </c>
+      <c r="C653" t="s">
+        <v>5</v>
+      </c>
+      <c r="D653" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A654">
+        <v>914</v>
+      </c>
+      <c r="B654" t="s">
+        <v>4</v>
+      </c>
+      <c r="C654" t="s">
+        <v>5</v>
+      </c>
+      <c r="D654" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A655">
+        <v>915</v>
+      </c>
+      <c r="B655" t="s">
+        <v>4</v>
+      </c>
+      <c r="C655" t="s">
+        <v>5</v>
+      </c>
+      <c r="D655" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A656">
+        <v>916</v>
+      </c>
+      <c r="B656" t="s">
+        <v>4</v>
+      </c>
+      <c r="C656" t="s">
+        <v>5</v>
+      </c>
+      <c r="D656" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A657">
+        <v>917</v>
+      </c>
+      <c r="B657" t="s">
+        <v>4</v>
+      </c>
+      <c r="C657" t="s">
+        <v>5</v>
+      </c>
+      <c r="D657" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A658">
+        <v>918</v>
+      </c>
+      <c r="B658" t="s">
+        <v>4</v>
+      </c>
+      <c r="C658" t="s">
+        <v>5</v>
+      </c>
+      <c r="D658" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A659">
+        <v>919</v>
+      </c>
+      <c r="B659" t="s">
+        <v>4</v>
+      </c>
+      <c r="C659" t="s">
+        <v>5</v>
+      </c>
+      <c r="D659" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A660">
+        <v>920</v>
+      </c>
+      <c r="B660" t="s">
+        <v>7</v>
+      </c>
+      <c r="C660" t="s">
+        <v>8</v>
+      </c>
+      <c r="D660" t="s">
+        <v>666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
